--- a/research/traditional_assets/database/data/bangladesh/bangladesh_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_farming_agriculture.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1145283573597535</v>
+        <v>0.1142162722876742</v>
       </c>
       <c r="C2">
-        <v>79.0256270008755</v>
+        <v>78.66722643150884</v>
       </c>
       <c r="D2">
-        <v>77.95562700087551</v>
+        <v>78.31122643150884</v>
       </c>
       <c r="E2">
-        <v>-43.70000000000001</v>
+        <v>-42.98600000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7140000000000001</v>
       </c>
       <c r="G2">
         <v>1.07</v>
@@ -1451,28 +1451,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0359142</v>
       </c>
       <c r="N2">
-        <v>5.586666666666668</v>
+        <v>5.550752466666668</v>
       </c>
       <c r="O2">
-        <v>1.676</v>
+        <v>1.66522574</v>
       </c>
       <c r="P2">
-        <v>3.910666666666668</v>
+        <v>3.885526726666668</v>
       </c>
       <c r="Q2">
-        <v>4.240666666666668</v>
+        <v>4.215526726666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1145283573597535</v>
+        <v>0.1150143154420952</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5928748568778965</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>155.5559268107508</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1142162722876742</v>
+        <v>0.113904187215595</v>
       </c>
       <c r="C3">
-        <v>78.66722643150884</v>
+        <v>78.31208490621793</v>
       </c>
       <c r="D3">
-        <v>78.31122643150884</v>
+        <v>78.67008490621794</v>
       </c>
       <c r="E3">
-        <v>-42.98600000000001</v>
+        <v>-42.27200000000001</v>
       </c>
       <c r="F3">
-        <v>0.7140000000000001</v>
+        <v>1.428</v>
       </c>
       <c r="G3">
         <v>1.07</v>
@@ -1533,28 +1533,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M3">
-        <v>0.0359142</v>
+        <v>0.0718284</v>
       </c>
       <c r="N3">
-        <v>5.550752466666668</v>
+        <v>5.514838266666668</v>
       </c>
       <c r="O3">
-        <v>1.66522574</v>
+        <v>1.65445148</v>
       </c>
       <c r="P3">
-        <v>3.885526726666668</v>
+        <v>3.860386786666667</v>
       </c>
       <c r="Q3">
-        <v>4.215526726666667</v>
+        <v>4.190386786666666</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1150143154420952</v>
+        <v>0.1155101910363214</v>
       </c>
       <c r="T3">
-        <v>0.5928748568778965</v>
+        <v>0.5971224199734539</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>155.5559268107508</v>
+        <v>77.77796340537542</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.113904187215595</v>
+        <v>0.1135921021435157</v>
       </c>
       <c r="C4">
-        <v>78.31208490621793</v>
+        <v>77.96024743462671</v>
       </c>
       <c r="D4">
-        <v>78.67008490621794</v>
+        <v>79.03224743462671</v>
       </c>
       <c r="E4">
-        <v>-42.27200000000001</v>
+        <v>-41.55800000000001</v>
       </c>
       <c r="F4">
-        <v>1.428</v>
+        <v>2.142</v>
       </c>
       <c r="G4">
         <v>1.07</v>
@@ -1615,28 +1615,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M4">
-        <v>0.0718284</v>
+        <v>0.1077426</v>
       </c>
       <c r="N4">
-        <v>5.514838266666668</v>
+        <v>5.478924066666668</v>
       </c>
       <c r="O4">
-        <v>1.65445148</v>
+        <v>1.64367722</v>
       </c>
       <c r="P4">
-        <v>3.860386786666667</v>
+        <v>3.835246846666668</v>
       </c>
       <c r="Q4">
-        <v>4.190386786666666</v>
+        <v>4.165246846666667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1155101910363214</v>
+        <v>0.1160162908696038</v>
       </c>
       <c r="T4">
-        <v>0.5971224199734539</v>
+        <v>0.6014575616895382</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.77796340537542</v>
+        <v>51.85197560358362</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1135921021435157</v>
+        <v>0.1132800170714365</v>
       </c>
       <c r="C5">
-        <v>77.96024743462671</v>
+        <v>77.61175985901021</v>
       </c>
       <c r="D5">
-        <v>79.03224743462671</v>
+        <v>79.39775985901021</v>
       </c>
       <c r="E5">
-        <v>-41.55800000000001</v>
+        <v>-40.84400000000001</v>
       </c>
       <c r="F5">
-        <v>2.142</v>
+        <v>2.856</v>
       </c>
       <c r="G5">
         <v>1.07</v>
@@ -1697,28 +1697,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M5">
-        <v>0.1077426</v>
+        <v>0.1436568</v>
       </c>
       <c r="N5">
-        <v>5.478924066666668</v>
+        <v>5.443009866666668</v>
       </c>
       <c r="O5">
-        <v>1.64367722</v>
+        <v>1.63290296</v>
       </c>
       <c r="P5">
-        <v>3.835246846666668</v>
+        <v>3.810106906666668</v>
       </c>
       <c r="Q5">
-        <v>4.165246846666667</v>
+        <v>4.140106906666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1160162908696038</v>
+        <v>0.116532934449413</v>
       </c>
       <c r="T5">
-        <v>0.6014575616895382</v>
+        <v>0.605883018858041</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.85197560358362</v>
+        <v>38.88898170268772</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1132800170714365</v>
+        <v>0.1129679319993572</v>
       </c>
       <c r="C6">
-        <v>77.61175985901021</v>
+        <v>77.26666887363891</v>
       </c>
       <c r="D6">
-        <v>79.39775985901021</v>
+        <v>79.76666887363892</v>
       </c>
       <c r="E6">
-        <v>-40.84400000000001</v>
+        <v>-40.13000000000001</v>
       </c>
       <c r="F6">
-        <v>2.856</v>
+        <v>3.57</v>
       </c>
       <c r="G6">
         <v>1.07</v>
@@ -1779,28 +1779,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M6">
-        <v>0.1436568</v>
+        <v>0.179571</v>
       </c>
       <c r="N6">
-        <v>5.443009866666668</v>
+        <v>5.407095666666668</v>
       </c>
       <c r="O6">
-        <v>1.63290296</v>
+        <v>1.6221287</v>
       </c>
       <c r="P6">
-        <v>3.810106906666668</v>
+        <v>3.784966966666667</v>
       </c>
       <c r="Q6">
-        <v>4.140106906666667</v>
+        <v>4.114966966666668</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.116532934449413</v>
+        <v>0.1170604547361655</v>
       </c>
       <c r="T6">
-        <v>0.605883018858041</v>
+        <v>0.6104016435458806</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.88898170268772</v>
+        <v>31.11118536215017</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1129679319993572</v>
+        <v>0.1126558469272779</v>
       </c>
       <c r="C7">
-        <v>77.26666887363891</v>
+        <v>76.92502204466416</v>
       </c>
       <c r="D7">
-        <v>79.76666887363892</v>
+        <v>80.13902204466417</v>
       </c>
       <c r="E7">
-        <v>-40.13000000000001</v>
+        <v>-39.41600000000001</v>
       </c>
       <c r="F7">
-        <v>3.57</v>
+        <v>4.284000000000001</v>
       </c>
       <c r="G7">
         <v>1.07</v>
@@ -1861,28 +1861,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M7">
-        <v>0.179571</v>
+        <v>0.2154852</v>
       </c>
       <c r="N7">
-        <v>5.407095666666668</v>
+        <v>5.371181466666668</v>
       </c>
       <c r="O7">
-        <v>1.6221287</v>
+        <v>1.61135444</v>
       </c>
       <c r="P7">
-        <v>3.784966966666667</v>
+        <v>3.759827026666668</v>
       </c>
       <c r="Q7">
-        <v>4.114966966666668</v>
+        <v>4.089827026666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1170604547361655</v>
+        <v>0.1175991988588063</v>
       </c>
       <c r="T7">
-        <v>0.6104016435458806</v>
+        <v>0.6150164091845253</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.11118536215017</v>
+        <v>25.92598780179181</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1126558469272779</v>
+        <v>0.1123437618551987</v>
       </c>
       <c r="C8">
-        <v>76.92502204466416</v>
+        <v>76.58686783056358</v>
       </c>
       <c r="D8">
-        <v>80.13902204466417</v>
+        <v>80.51486783056359</v>
       </c>
       <c r="E8">
-        <v>-39.41600000000001</v>
+        <v>-38.70200000000001</v>
       </c>
       <c r="F8">
-        <v>4.284</v>
+        <v>4.998</v>
       </c>
       <c r="G8">
         <v>1.07</v>
@@ -1943,28 +1943,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M8">
-        <v>0.2154852</v>
+        <v>0.2513994</v>
       </c>
       <c r="N8">
-        <v>5.371181466666668</v>
+        <v>5.335267266666667</v>
       </c>
       <c r="O8">
-        <v>1.61135444</v>
+        <v>1.60058018</v>
       </c>
       <c r="P8">
-        <v>3.759827026666668</v>
+        <v>3.734687086666667</v>
       </c>
       <c r="Q8">
-        <v>4.089827026666667</v>
+        <v>4.064687086666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1175991988588063</v>
+        <v>0.1181495288765577</v>
       </c>
       <c r="T8">
-        <v>0.6150164091845253</v>
+        <v>0.6197304170949689</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.92598780179181</v>
+        <v>22.22227525867869</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1123437618551987</v>
+        <v>0.1120316767831194</v>
       </c>
       <c r="C9">
-        <v>76.58686783056359</v>
+        <v>76.25225560316422</v>
       </c>
       <c r="D9">
-        <v>80.5148678305636</v>
+        <v>80.89425560316423</v>
       </c>
       <c r="E9">
-        <v>-38.70200000000001</v>
+        <v>-37.98800000000001</v>
       </c>
       <c r="F9">
-        <v>4.998000000000001</v>
+        <v>5.712000000000001</v>
       </c>
       <c r="G9">
         <v>1.07</v>
@@ -2025,28 +2025,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M9">
-        <v>0.2513994000000001</v>
+        <v>0.2873136</v>
       </c>
       <c r="N9">
-        <v>5.335267266666667</v>
+        <v>5.299353066666668</v>
       </c>
       <c r="O9">
-        <v>1.60058018</v>
+        <v>1.58980592</v>
       </c>
       <c r="P9">
-        <v>3.734687086666667</v>
+        <v>3.709547146666667</v>
       </c>
       <c r="Q9">
-        <v>4.064687086666667</v>
+        <v>4.039547146666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1181495288765577</v>
+        <v>0.1187118225903472</v>
       </c>
       <c r="T9">
-        <v>0.6197304170949689</v>
+        <v>0.6245469034382483</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.22227525867869</v>
+        <v>19.44449085134385</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1120316767831194</v>
+        <v>0.1117195917110402</v>
       </c>
       <c r="C10">
-        <v>76.25225560316422</v>
+        <v>75.9212356692632</v>
       </c>
       <c r="D10">
-        <v>80.89425560316423</v>
+        <v>81.27723566926321</v>
       </c>
       <c r="E10">
-        <v>-37.98800000000001</v>
+        <v>-37.27400000000001</v>
       </c>
       <c r="F10">
-        <v>5.712000000000001</v>
+        <v>6.426</v>
       </c>
       <c r="G10">
         <v>1.07</v>
@@ -2107,28 +2107,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M10">
-        <v>0.2873136</v>
+        <v>0.3232278</v>
       </c>
       <c r="N10">
-        <v>5.299353066666668</v>
+        <v>5.263438866666668</v>
       </c>
       <c r="O10">
-        <v>1.58980592</v>
+        <v>1.57903166</v>
       </c>
       <c r="P10">
-        <v>3.709547146666667</v>
+        <v>3.684407206666668</v>
       </c>
       <c r="Q10">
-        <v>4.039547146666667</v>
+        <v>4.014407206666668</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1187118225903472</v>
+        <v>0.1192864744077364</v>
       </c>
       <c r="T10">
-        <v>0.6245469034382483</v>
+        <v>0.6294692466242369</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.44449085134385</v>
+        <v>17.2839918678612</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1117195917110402</v>
+        <v>0.1114075066389609</v>
       </c>
       <c r="C11">
-        <v>75.9212356692632</v>
+        <v>75.59385929286516</v>
       </c>
       <c r="D11">
-        <v>81.27723566926321</v>
+        <v>81.66385929286517</v>
       </c>
       <c r="E11">
-        <v>-37.27400000000001</v>
+        <v>-36.56000000000001</v>
       </c>
       <c r="F11">
-        <v>6.426</v>
+        <v>7.14</v>
       </c>
       <c r="G11">
         <v>1.07</v>
@@ -2189,28 +2189,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M11">
-        <v>0.3232278</v>
+        <v>0.359142</v>
       </c>
       <c r="N11">
-        <v>5.263438866666668</v>
+        <v>5.227524666666667</v>
       </c>
       <c r="O11">
-        <v>1.57903166</v>
+        <v>1.5682574</v>
       </c>
       <c r="P11">
-        <v>3.684407206666668</v>
+        <v>3.659267266666667</v>
       </c>
       <c r="Q11">
-        <v>4.014407206666668</v>
+        <v>3.989267266666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1192864744077364</v>
+        <v>0.1198738962655121</v>
       </c>
       <c r="T11">
-        <v>0.6294692466242369</v>
+        <v>0.6345009752143587</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.2839918678612</v>
+        <v>15.55559268107509</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1114075066389609</v>
+        <v>0.1110954215668816</v>
       </c>
       <c r="C12">
-        <v>75.59385929286516</v>
+        <v>75.27017871805762</v>
       </c>
       <c r="D12">
-        <v>81.66385929286517</v>
+        <v>82.05417871805763</v>
       </c>
       <c r="E12">
-        <v>-36.56000000000001</v>
+        <v>-35.84600000000001</v>
       </c>
       <c r="F12">
-        <v>7.140000000000001</v>
+        <v>7.854000000000001</v>
       </c>
       <c r="G12">
         <v>1.07</v>
@@ -2271,28 +2271,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M12">
-        <v>0.359142</v>
+        <v>0.3950562</v>
       </c>
       <c r="N12">
-        <v>5.227524666666667</v>
+        <v>5.191610466666668</v>
       </c>
       <c r="O12">
-        <v>1.5682574</v>
+        <v>1.55748314</v>
       </c>
       <c r="P12">
-        <v>3.659267266666667</v>
+        <v>3.634127326666667</v>
       </c>
       <c r="Q12">
-        <v>3.989267266666667</v>
+        <v>3.964127326666667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1198738962655121</v>
+        <v>0.1204745186144738</v>
       </c>
       <c r="T12">
-        <v>0.6345009752143587</v>
+        <v>0.6396457763570675</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.55559268107508</v>
+        <v>14.14144789188644</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1110954215668816</v>
+        <v>0.1107833364948024</v>
       </c>
       <c r="C13">
-        <v>75.27017871805762</v>
+        <v>74.95024719254536</v>
       </c>
       <c r="D13">
-        <v>82.05417871805763</v>
+        <v>82.44824719254537</v>
       </c>
       <c r="E13">
-        <v>-35.84600000000001</v>
+        <v>-35.13200000000001</v>
       </c>
       <c r="F13">
-        <v>7.854000000000001</v>
+        <v>8.568</v>
       </c>
       <c r="G13">
         <v>1.07</v>
@@ -2353,28 +2353,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M13">
-        <v>0.3950562</v>
+        <v>0.4309704</v>
       </c>
       <c r="N13">
-        <v>5.191610466666668</v>
+        <v>5.155696266666668</v>
       </c>
       <c r="O13">
-        <v>1.55748314</v>
+        <v>1.54670888</v>
       </c>
       <c r="P13">
-        <v>3.634127326666667</v>
+        <v>3.608987386666668</v>
       </c>
       <c r="Q13">
-        <v>3.964127326666667</v>
+        <v>3.938987386666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1204745186144738</v>
+        <v>0.1210887914713663</v>
       </c>
       <c r="T13">
-        <v>0.6396457763570675</v>
+        <v>0.6449075047984743</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.14144789188644</v>
+        <v>12.9629939008959</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1107833364948024</v>
+        <v>0.1106077514227231</v>
       </c>
       <c r="C14">
-        <v>74.95024719254536</v>
+        <v>74.45962604936891</v>
       </c>
       <c r="D14">
-        <v>82.44824719254537</v>
+        <v>82.67162604936891</v>
       </c>
       <c r="E14">
-        <v>-35.13200000000001</v>
+        <v>-34.41800000000001</v>
       </c>
       <c r="F14">
-        <v>8.568</v>
+        <v>9.282000000000002</v>
       </c>
       <c r="G14">
         <v>1.07</v>
@@ -2435,45 +2435,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M14">
-        <v>0.4309704</v>
+        <v>0.4808076000000001</v>
       </c>
       <c r="N14">
-        <v>5.155696266666668</v>
+        <v>5.105859066666667</v>
       </c>
       <c r="O14">
-        <v>1.54670888</v>
+        <v>1.53175772</v>
       </c>
       <c r="P14">
-        <v>3.608987386666668</v>
+        <v>3.574101346666668</v>
       </c>
       <c r="Q14">
-        <v>3.938987386666667</v>
+        <v>3.904101346666667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1210887914713663</v>
+        <v>0.1217171855433599</v>
       </c>
       <c r="T14">
-        <v>0.6449075047984743</v>
+        <v>0.650290192514396</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>12.9629939008959</v>
+        <v>11.61933935043179</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1106077514227231</v>
+        <v>0.1103061663506438</v>
       </c>
       <c r="C15">
-        <v>74.45962604936891</v>
+        <v>74.13213992411198</v>
       </c>
       <c r="D15">
-        <v>82.67162604936891</v>
+        <v>83.05813992411198</v>
       </c>
       <c r="E15">
-        <v>-34.41800000000001</v>
+        <v>-33.70400000000001</v>
       </c>
       <c r="F15">
-        <v>9.282000000000002</v>
+        <v>9.996000000000002</v>
       </c>
       <c r="G15">
         <v>1.07</v>
@@ -2517,28 +2517,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M15">
-        <v>0.4808076000000001</v>
+        <v>0.5177928000000001</v>
       </c>
       <c r="N15">
-        <v>5.105859066666667</v>
+        <v>5.068873866666667</v>
       </c>
       <c r="O15">
-        <v>1.53175772</v>
+        <v>1.52066216</v>
       </c>
       <c r="P15">
-        <v>3.574101346666668</v>
+        <v>3.548211706666667</v>
       </c>
       <c r="Q15">
-        <v>3.904101346666667</v>
+        <v>3.878211706666667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1217171855433599</v>
+        <v>0.1223601934309812</v>
       </c>
       <c r="T15">
-        <v>0.650290192514396</v>
+        <v>0.655798059014409</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.61933935043179</v>
+        <v>10.78938653968666</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1103061663506438</v>
+        <v>0.1100045812785646</v>
       </c>
       <c r="C16">
-        <v>74.13213992411198</v>
+        <v>73.80828490468744</v>
       </c>
       <c r="D16">
-        <v>83.05813992411198</v>
+        <v>83.44828490468745</v>
       </c>
       <c r="E16">
-        <v>-33.70400000000001</v>
+        <v>-32.99000000000001</v>
       </c>
       <c r="F16">
-        <v>9.996000000000002</v>
+        <v>10.71</v>
       </c>
       <c r="G16">
         <v>1.07</v>
@@ -2599,28 +2599,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M16">
-        <v>0.5177928000000001</v>
+        <v>0.5547780000000001</v>
       </c>
       <c r="N16">
-        <v>5.068873866666667</v>
+        <v>5.031888666666668</v>
       </c>
       <c r="O16">
-        <v>1.52066216</v>
+        <v>1.5095666</v>
       </c>
       <c r="P16">
-        <v>3.548211706666667</v>
+        <v>3.522322066666668</v>
       </c>
       <c r="Q16">
-        <v>3.878211706666667</v>
+        <v>3.852322066666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1223601934309812</v>
+        <v>0.1230183309159583</v>
       </c>
       <c r="T16">
-        <v>0.655798059014409</v>
+        <v>0.661435522373246</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.78938653968666</v>
+        <v>10.07009410370755</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1100045812785646</v>
+        <v>0.1098933962064853</v>
       </c>
       <c r="C17">
-        <v>73.80828490468744</v>
+        <v>73.23904558396441</v>
       </c>
       <c r="D17">
-        <v>83.44828490468745</v>
+        <v>83.59304558396443</v>
       </c>
       <c r="E17">
-        <v>-32.99000000000001</v>
+        <v>-32.27600000000001</v>
       </c>
       <c r="F17">
-        <v>10.71</v>
+        <v>11.424</v>
       </c>
       <c r="G17">
         <v>1.07</v>
@@ -2681,45 +2681,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M17">
-        <v>0.554778</v>
+        <v>0.6111840000000001</v>
       </c>
       <c r="N17">
-        <v>5.031888666666668</v>
+        <v>4.975482666666668</v>
       </c>
       <c r="O17">
-        <v>1.5095666</v>
+        <v>1.4926448</v>
       </c>
       <c r="P17">
-        <v>3.522322066666668</v>
+        <v>3.482837866666668</v>
       </c>
       <c r="Q17">
-        <v>3.852322066666667</v>
+        <v>3.812837866666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1230183309159583</v>
+        <v>0.123692138341054</v>
       </c>
       <c r="T17">
-        <v>0.661435522373246</v>
+        <v>0.6672072110501504</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.07009410370755</v>
+        <v>9.140727942267251</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1098933962064853</v>
+        <v>0.1096037111344061</v>
       </c>
       <c r="C18">
-        <v>73.23904558396441</v>
+        <v>72.90457926632818</v>
       </c>
       <c r="D18">
-        <v>83.59304558396443</v>
+        <v>83.9725792663282</v>
       </c>
       <c r="E18">
-        <v>-32.27600000000001</v>
+        <v>-31.56200000000001</v>
       </c>
       <c r="F18">
-        <v>11.424</v>
+        <v>12.138</v>
       </c>
       <c r="G18">
         <v>1.07</v>
@@ -2763,28 +2763,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M18">
-        <v>0.6111840000000001</v>
+        <v>0.649383</v>
       </c>
       <c r="N18">
-        <v>4.975482666666668</v>
+        <v>4.937283666666668</v>
       </c>
       <c r="O18">
-        <v>1.4926448</v>
+        <v>1.4811851</v>
       </c>
       <c r="P18">
-        <v>3.482837866666668</v>
+        <v>3.456098566666667</v>
       </c>
       <c r="Q18">
-        <v>3.812837866666667</v>
+        <v>3.786098566666667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.123692138341054</v>
+        <v>0.1243821820896459</v>
       </c>
       <c r="T18">
-        <v>0.6672072110501504</v>
+        <v>0.6731179765626429</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.140727942267251</v>
+        <v>8.603038063310354</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1096037111344061</v>
+        <v>0.1093140260623268</v>
       </c>
       <c r="C19">
-        <v>72.90457926632818</v>
+        <v>72.57357502625023</v>
       </c>
       <c r="D19">
-        <v>83.9725792663282</v>
+        <v>84.35557502625024</v>
       </c>
       <c r="E19">
-        <v>-31.56200000000001</v>
+        <v>-30.84800000000001</v>
       </c>
       <c r="F19">
-        <v>12.138</v>
+        <v>12.852</v>
       </c>
       <c r="G19">
         <v>1.07</v>
@@ -2845,28 +2845,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M19">
-        <v>0.649383</v>
+        <v>0.6875820000000001</v>
       </c>
       <c r="N19">
-        <v>4.937283666666668</v>
+        <v>4.899084666666668</v>
       </c>
       <c r="O19">
-        <v>1.4811851</v>
+        <v>1.4697254</v>
       </c>
       <c r="P19">
-        <v>3.456098566666667</v>
+        <v>3.429359266666667</v>
       </c>
       <c r="Q19">
-        <v>3.786098566666667</v>
+        <v>3.759359266666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1243821820896459</v>
+        <v>0.1250890561735693</v>
       </c>
       <c r="T19">
-        <v>0.6731179765626429</v>
+        <v>0.6791729070876351</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.603038063310354</v>
+        <v>8.125091504237556</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1093140260623268</v>
+        <v>0.1090243409902475</v>
       </c>
       <c r="C20">
-        <v>72.57357502625021</v>
+        <v>72.24608045199338</v>
       </c>
       <c r="D20">
-        <v>84.35557502625022</v>
+        <v>84.74208045199339</v>
       </c>
       <c r="E20">
-        <v>-30.84800000000001</v>
+        <v>-30.13400000000001</v>
       </c>
       <c r="F20">
-        <v>12.852</v>
+        <v>13.566</v>
       </c>
       <c r="G20">
         <v>1.07</v>
@@ -2927,28 +2927,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M20">
-        <v>0.687582</v>
+        <v>0.725781</v>
       </c>
       <c r="N20">
-        <v>4.899084666666668</v>
+        <v>4.860885666666668</v>
       </c>
       <c r="O20">
-        <v>1.4697254</v>
+        <v>1.4582657</v>
       </c>
       <c r="P20">
-        <v>3.429359266666667</v>
+        <v>3.402619966666668</v>
       </c>
       <c r="Q20">
-        <v>3.759359266666667</v>
+        <v>3.732619966666668</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1250890561735693</v>
+        <v>0.1258133839385772</v>
       </c>
       <c r="T20">
-        <v>0.6791729070876351</v>
+        <v>0.6853773420700346</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.125091504237556</v>
+        <v>7.697455109277686</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1090243409902475</v>
+        <v>0.1088466559181683</v>
       </c>
       <c r="C21">
-        <v>72.24608045199338</v>
+        <v>71.77090997362261</v>
       </c>
       <c r="D21">
-        <v>84.74208045199339</v>
+        <v>84.98090997362262</v>
       </c>
       <c r="E21">
-        <v>-30.13400000000001</v>
+        <v>-29.42000000000001</v>
       </c>
       <c r="F21">
-        <v>13.566</v>
+        <v>14.28</v>
       </c>
       <c r="G21">
         <v>1.07</v>
@@ -3009,45 +3009,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M21">
-        <v>0.725781</v>
+        <v>0.7754040000000001</v>
       </c>
       <c r="N21">
-        <v>4.860885666666668</v>
+        <v>4.811262666666668</v>
       </c>
       <c r="O21">
-        <v>1.4582657</v>
+        <v>1.4433788</v>
       </c>
       <c r="P21">
-        <v>3.402619966666668</v>
+        <v>3.367883866666667</v>
       </c>
       <c r="Q21">
-        <v>3.732619966666668</v>
+        <v>3.697883866666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1258133839385772</v>
+        <v>0.1265558198977104</v>
       </c>
       <c r="T21">
-        <v>0.6853773420700346</v>
+        <v>0.6917368879269942</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.697455109277686</v>
+        <v>7.204846333868109</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1088466559181683</v>
+        <v>0.108562570846089</v>
       </c>
       <c r="C22">
-        <v>71.77090997362261</v>
+        <v>71.44156292218362</v>
       </c>
       <c r="D22">
-        <v>84.98090997362262</v>
+        <v>85.36556292218363</v>
       </c>
       <c r="E22">
-        <v>-29.42000000000001</v>
+        <v>-28.70600000000001</v>
       </c>
       <c r="F22">
-        <v>14.28</v>
+        <v>14.994</v>
       </c>
       <c r="G22">
         <v>1.07</v>
@@ -3091,28 +3091,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M22">
-        <v>0.7754040000000001</v>
+        <v>0.8141742000000002</v>
       </c>
       <c r="N22">
-        <v>4.811262666666668</v>
+        <v>4.772492466666668</v>
       </c>
       <c r="O22">
-        <v>1.4433788</v>
+        <v>1.43174774</v>
       </c>
       <c r="P22">
-        <v>3.367883866666667</v>
+        <v>3.340744726666667</v>
       </c>
       <c r="Q22">
-        <v>3.697883866666667</v>
+        <v>3.670744726666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1265558198977104</v>
+        <v>0.1273170517039102</v>
       </c>
       <c r="T22">
-        <v>0.6917368879269942</v>
+        <v>0.6982574349448893</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.204846333868109</v>
+        <v>6.861758413207722</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.108562570846089</v>
+        <v>0.1082784857740098</v>
       </c>
       <c r="C23">
-        <v>71.44156292218362</v>
+        <v>71.11571384798475</v>
       </c>
       <c r="D23">
-        <v>85.36556292218363</v>
+        <v>85.75371384798476</v>
       </c>
       <c r="E23">
-        <v>-28.70600000000001</v>
+        <v>-27.99200000000001</v>
       </c>
       <c r="F23">
-        <v>14.994</v>
+        <v>15.708</v>
       </c>
       <c r="G23">
         <v>1.07</v>
@@ -3173,28 +3173,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M23">
-        <v>0.8141742</v>
+        <v>0.8529444000000002</v>
       </c>
       <c r="N23">
-        <v>4.772492466666668</v>
+        <v>4.733722266666668</v>
       </c>
       <c r="O23">
-        <v>1.43174774</v>
+        <v>1.42011668</v>
       </c>
       <c r="P23">
-        <v>3.340744726666667</v>
+        <v>3.313605586666667</v>
       </c>
       <c r="Q23">
-        <v>3.670744726666667</v>
+        <v>3.643605586666667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1273170517039102</v>
+        <v>0.1280978022743715</v>
       </c>
       <c r="T23">
-        <v>0.6982574349448892</v>
+        <v>0.7049451754760638</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.861758413207724</v>
+        <v>6.549860303516462</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1082784857740098</v>
+        <v>0.1079944007019305</v>
       </c>
       <c r="C24">
-        <v>71.11571384798475</v>
+        <v>70.79341068410868</v>
       </c>
       <c r="D24">
-        <v>85.75371384798476</v>
+        <v>86.14541068410868</v>
       </c>
       <c r="E24">
-        <v>-27.99200000000001</v>
+        <v>-27.27800000000001</v>
       </c>
       <c r="F24">
-        <v>15.708</v>
+        <v>16.422</v>
       </c>
       <c r="G24">
         <v>1.07</v>
@@ -3255,28 +3255,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M24">
-        <v>0.8529444000000002</v>
+        <v>0.8917146</v>
       </c>
       <c r="N24">
-        <v>4.733722266666668</v>
+        <v>4.694952066666668</v>
       </c>
       <c r="O24">
-        <v>1.42011668</v>
+        <v>1.40848562</v>
       </c>
       <c r="P24">
-        <v>3.313605586666667</v>
+        <v>3.286466446666667</v>
       </c>
       <c r="Q24">
-        <v>3.643605586666667</v>
+        <v>3.616466446666667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1280978022743715</v>
+        <v>0.1288988320804292</v>
       </c>
       <c r="T24">
-        <v>0.7049451754760638</v>
+        <v>0.7118066235535027</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.549860303516462</v>
+        <v>6.265083768580965</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1079944007019305</v>
+        <v>0.1078783156298513</v>
       </c>
       <c r="C25">
-        <v>70.79341068410868</v>
+        <v>70.24050068964601</v>
       </c>
       <c r="D25">
-        <v>86.14541068410868</v>
+        <v>86.30650068964603</v>
       </c>
       <c r="E25">
-        <v>-27.27800000000001</v>
+        <v>-26.56400000000001</v>
       </c>
       <c r="F25">
-        <v>16.422</v>
+        <v>17.136</v>
       </c>
       <c r="G25">
         <v>1.07</v>
@@ -3337,45 +3337,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M25">
-        <v>0.8917146</v>
+        <v>0.9476208000000002</v>
       </c>
       <c r="N25">
-        <v>4.694952066666668</v>
+        <v>4.639045866666668</v>
       </c>
       <c r="O25">
-        <v>1.40848562</v>
+        <v>1.39171376</v>
       </c>
       <c r="P25">
-        <v>3.286466446666667</v>
+        <v>3.247332106666668</v>
       </c>
       <c r="Q25">
-        <v>3.616466446666667</v>
+        <v>3.577332106666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1288988320804292</v>
+        <v>0.1297209416182253</v>
       </c>
       <c r="T25">
-        <v>0.7118066235535027</v>
+        <v>0.718848636054032</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.265083768580965</v>
+        <v>5.895466484765496</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1078783156298513</v>
+        <v>0.107601230557772</v>
       </c>
       <c r="C26">
-        <v>70.24050068964603</v>
+        <v>69.91345484490583</v>
       </c>
       <c r="D26">
-        <v>86.30650068964603</v>
+        <v>86.69345484490583</v>
       </c>
       <c r="E26">
-        <v>-26.56400000000001</v>
+        <v>-25.85000000000001</v>
       </c>
       <c r="F26">
-        <v>17.136</v>
+        <v>17.85</v>
       </c>
       <c r="G26">
         <v>1.07</v>
@@ -3419,28 +3419,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M26">
-        <v>0.9476208</v>
+        <v>0.9871050000000001</v>
       </c>
       <c r="N26">
-        <v>4.639045866666668</v>
+        <v>4.599561666666668</v>
       </c>
       <c r="O26">
-        <v>1.39171376</v>
+        <v>1.3798685</v>
       </c>
       <c r="P26">
-        <v>3.247332106666668</v>
+        <v>3.219693166666667</v>
       </c>
       <c r="Q26">
-        <v>3.577332106666667</v>
+        <v>3.549693166666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1297209416182253</v>
+        <v>0.1305649740770293</v>
       </c>
       <c r="T26">
-        <v>0.718848636054032</v>
+        <v>0.7260784355545755</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.895466484765496</v>
+        <v>5.659647825374877</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.107601230557772</v>
+        <v>0.1073241454856927</v>
       </c>
       <c r="C27">
-        <v>69.91345484490583</v>
+        <v>69.58989443565297</v>
       </c>
       <c r="D27">
-        <v>86.69345484490583</v>
+        <v>87.08389443565298</v>
       </c>
       <c r="E27">
-        <v>-25.85000000000001</v>
+        <v>-25.13600000000001</v>
       </c>
       <c r="F27">
-        <v>17.85</v>
+        <v>18.564</v>
       </c>
       <c r="G27">
         <v>1.07</v>
@@ -3501,28 +3501,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M27">
-        <v>0.9871050000000001</v>
+        <v>1.0265892</v>
       </c>
       <c r="N27">
-        <v>4.599561666666668</v>
+        <v>4.560077466666668</v>
       </c>
       <c r="O27">
-        <v>1.3798685</v>
+        <v>1.36802324</v>
       </c>
       <c r="P27">
-        <v>3.219693166666667</v>
+        <v>3.192054226666667</v>
       </c>
       <c r="Q27">
-        <v>3.549693166666667</v>
+        <v>3.522054226666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1305649740770293</v>
+        <v>0.1314318182239091</v>
       </c>
       <c r="T27">
-        <v>0.7260784355545755</v>
+        <v>0.73350363504162</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.659647825374877</v>
+        <v>5.441969062860457</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1073241454856927</v>
+        <v>0.1070470604136135</v>
       </c>
       <c r="C28">
-        <v>69.58989443565297</v>
+        <v>69.2698667667933</v>
       </c>
       <c r="D28">
-        <v>87.08389443565298</v>
+        <v>87.47786676679331</v>
       </c>
       <c r="E28">
-        <v>-25.13600000000001</v>
+        <v>-24.42200000000001</v>
       </c>
       <c r="F28">
-        <v>18.564</v>
+        <v>19.278</v>
       </c>
       <c r="G28">
         <v>1.07</v>
@@ -3583,28 +3583,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M28">
-        <v>1.0265892</v>
+        <v>1.0660734</v>
       </c>
       <c r="N28">
-        <v>4.560077466666668</v>
+        <v>4.520593266666667</v>
       </c>
       <c r="O28">
-        <v>1.36802324</v>
+        <v>1.35617798</v>
       </c>
       <c r="P28">
-        <v>3.192054226666667</v>
+        <v>3.164415286666667</v>
       </c>
       <c r="Q28">
-        <v>3.522054226666667</v>
+        <v>3.494415286666667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1314318182239091</v>
+        <v>0.1323224115254979</v>
       </c>
       <c r="T28">
-        <v>0.73350363504162</v>
+        <v>0.7411322646515974</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.441969062860457</v>
+        <v>5.240414653124885</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1070470604136135</v>
+        <v>0.1067699753415342</v>
       </c>
       <c r="C29">
-        <v>69.2698667667933</v>
+        <v>68.95342000316317</v>
       </c>
       <c r="D29">
-        <v>87.47786676679331</v>
+        <v>87.87542000316319</v>
       </c>
       <c r="E29">
-        <v>-24.42200000000001</v>
+        <v>-23.70800000000001</v>
       </c>
       <c r="F29">
-        <v>19.278</v>
+        <v>19.992</v>
       </c>
       <c r="G29">
         <v>1.07</v>
@@ -3665,28 +3665,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M29">
-        <v>1.0660734</v>
+        <v>1.1055576</v>
       </c>
       <c r="N29">
-        <v>4.520593266666667</v>
+        <v>4.481109066666668</v>
       </c>
       <c r="O29">
-        <v>1.35617798</v>
+        <v>1.34433272</v>
       </c>
       <c r="P29">
-        <v>3.164415286666667</v>
+        <v>3.136776346666667</v>
       </c>
       <c r="Q29">
-        <v>3.494415286666667</v>
+        <v>3.466776346666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1323224115254979</v>
+        <v>0.1332377435299086</v>
       </c>
       <c r="T29">
-        <v>0.7411322646515974</v>
+        <v>0.7489728006396296</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.240414653124885</v>
+        <v>5.053256986941854</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1067699753415342</v>
+        <v>0.106492890269455</v>
       </c>
       <c r="C30">
-        <v>68.95342000316317</v>
+        <v>68.6406031891586</v>
       </c>
       <c r="D30">
-        <v>87.87542000316319</v>
+        <v>88.27660318915861</v>
       </c>
       <c r="E30">
-        <v>-23.70800000000001</v>
+        <v>-22.99400000000001</v>
       </c>
       <c r="F30">
-        <v>19.992</v>
+        <v>20.706</v>
       </c>
       <c r="G30">
         <v>1.07</v>
@@ -3747,28 +3747,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M30">
-        <v>1.1055576</v>
+        <v>1.1450418</v>
       </c>
       <c r="N30">
-        <v>4.481109066666668</v>
+        <v>4.441624866666667</v>
       </c>
       <c r="O30">
-        <v>1.34433272</v>
+        <v>1.33248746</v>
       </c>
       <c r="P30">
-        <v>3.136776346666667</v>
+        <v>3.109137406666667</v>
       </c>
       <c r="Q30">
-        <v>3.466776346666667</v>
+        <v>3.439137406666667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1332377435299086</v>
+        <v>0.1341788595344436</v>
       </c>
       <c r="T30">
-        <v>0.7489728006396296</v>
+        <v>0.7570341967963389</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.053256986941854</v>
+        <v>4.879006746012823</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.106492890269455</v>
+        <v>0.1062158051973757</v>
       </c>
       <c r="C31">
-        <v>68.6406031891586</v>
+        <v>68.3314662689052</v>
       </c>
       <c r="D31">
-        <v>88.27660318915861</v>
+        <v>88.68146626890521</v>
       </c>
       <c r="E31">
-        <v>-22.99400000000001</v>
+        <v>-22.28000000000001</v>
       </c>
       <c r="F31">
-        <v>20.706</v>
+        <v>21.42</v>
       </c>
       <c r="G31">
         <v>1.07</v>
@@ -3829,28 +3829,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M31">
-        <v>1.1450418</v>
+        <v>1.184526</v>
       </c>
       <c r="N31">
-        <v>4.441624866666668</v>
+        <v>4.402140666666668</v>
       </c>
       <c r="O31">
-        <v>1.332487460000001</v>
+        <v>1.3206422</v>
       </c>
       <c r="P31">
-        <v>3.109137406666668</v>
+        <v>3.081498466666668</v>
       </c>
       <c r="Q31">
-        <v>3.439137406666668</v>
+        <v>3.411498466666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1341788595344436</v>
+        <v>0.1351468645676796</v>
       </c>
       <c r="T31">
-        <v>0.7570341967963389</v>
+        <v>0.7653259185575255</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.879006746012825</v>
+        <v>4.716373187812397</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1062158051973757</v>
+        <v>0.1059387201252964</v>
       </c>
       <c r="C32">
-        <v>68.3314662689052</v>
+        <v>68.02606010698523</v>
       </c>
       <c r="D32">
-        <v>88.68146626890521</v>
+        <v>89.09006010698523</v>
       </c>
       <c r="E32">
-        <v>-22.28000000000001</v>
+        <v>-21.56600000000001</v>
       </c>
       <c r="F32">
-        <v>21.42</v>
+        <v>22.134</v>
       </c>
       <c r="G32">
         <v>1.07</v>
@@ -3911,28 +3911,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M32">
-        <v>1.184526</v>
+        <v>1.2240102</v>
       </c>
       <c r="N32">
-        <v>4.402140666666668</v>
+        <v>4.362656466666667</v>
       </c>
       <c r="O32">
-        <v>1.3206422</v>
+        <v>1.30879694</v>
       </c>
       <c r="P32">
-        <v>3.081498466666668</v>
+        <v>3.053859526666667</v>
       </c>
       <c r="Q32">
-        <v>3.411498466666667</v>
+        <v>3.383859526666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1351468645676796</v>
+        <v>0.1361429277178209</v>
       </c>
       <c r="T32">
-        <v>0.7653259185575255</v>
+        <v>0.7738579800799058</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.716373187812397</v>
+        <v>4.564232117237803</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1059387201252964</v>
+        <v>0.1062216350532172</v>
       </c>
       <c r="C33">
-        <v>68.02606010698523</v>
+        <v>66.89490972845901</v>
       </c>
       <c r="D33">
-        <v>89.09006010698523</v>
+        <v>88.67290972845902</v>
       </c>
       <c r="E33">
-        <v>-21.56600000000001</v>
+        <v>-20.85200000000001</v>
       </c>
       <c r="F33">
-        <v>22.134</v>
+        <v>22.848</v>
       </c>
       <c r="G33">
         <v>1.07</v>
@@ -3993,45 +3993,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M33">
-        <v>1.2240102</v>
+        <v>1.3206144</v>
       </c>
       <c r="N33">
-        <v>4.362656466666667</v>
+        <v>4.266052266666668</v>
       </c>
       <c r="O33">
-        <v>1.30879694</v>
+        <v>1.27981568</v>
       </c>
       <c r="P33">
-        <v>3.053859526666667</v>
+        <v>2.986236586666667</v>
       </c>
       <c r="Q33">
-        <v>3.383859526666667</v>
+        <v>3.316236586666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1361429277178209</v>
+        <v>0.1371682868429664</v>
       </c>
       <c r="T33">
-        <v>0.7738579800799058</v>
+        <v>0.7826409845882386</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.564232117237803</v>
+        <v>4.23035419473441</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1062216350532172</v>
+        <v>0.1059620499811379</v>
       </c>
       <c r="C34">
-        <v>66.89490972845901</v>
+        <v>66.56351244346882</v>
       </c>
       <c r="D34">
-        <v>88.67290972845902</v>
+        <v>89.05551244346884</v>
       </c>
       <c r="E34">
-        <v>-20.85200000000001</v>
+        <v>-20.13800000000001</v>
       </c>
       <c r="F34">
-        <v>22.848</v>
+        <v>23.562</v>
       </c>
       <c r="G34">
         <v>1.07</v>
@@ -4075,28 +4075,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M34">
-        <v>1.3206144</v>
+        <v>1.3618836</v>
       </c>
       <c r="N34">
-        <v>4.266052266666668</v>
+        <v>4.224783066666667</v>
       </c>
       <c r="O34">
-        <v>1.27981568</v>
+        <v>1.26743492</v>
       </c>
       <c r="P34">
-        <v>2.986236586666667</v>
+        <v>2.957348146666667</v>
       </c>
       <c r="Q34">
-        <v>3.316236586666667</v>
+        <v>3.287348146666667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1371682868429664</v>
+        <v>0.1382242537031909</v>
       </c>
       <c r="T34">
-        <v>0.7826409845882386</v>
+        <v>0.7916861683356263</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.23035419473441</v>
+        <v>4.102161643378822</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1059620499811379</v>
+        <v>0.1065354649090586</v>
       </c>
       <c r="C35">
-        <v>66.56351244346882</v>
+        <v>65.00872262939268</v>
       </c>
       <c r="D35">
-        <v>89.05551244346884</v>
+        <v>88.21472262939268</v>
       </c>
       <c r="E35">
-        <v>-20.13800000000001</v>
+        <v>-19.42400000000001</v>
       </c>
       <c r="F35">
-        <v>23.562</v>
+        <v>24.276</v>
       </c>
       <c r="G35">
         <v>1.07</v>
@@ -4157,45 +4157,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M35">
-        <v>1.3618836</v>
+        <v>1.4881188</v>
       </c>
       <c r="N35">
-        <v>4.224783066666667</v>
+        <v>4.098547866666667</v>
       </c>
       <c r="O35">
-        <v>1.26743492</v>
+        <v>1.22956436</v>
       </c>
       <c r="P35">
-        <v>2.957348146666667</v>
+        <v>2.868983506666667</v>
       </c>
       <c r="Q35">
-        <v>3.287348146666667</v>
+        <v>3.198983506666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1382242537031909</v>
+        <v>0.1393122195591798</v>
       </c>
       <c r="T35">
-        <v>0.7916861683356263</v>
+        <v>0.8010054485602073</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.102161643378822</v>
+        <v>3.75418055780672</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1065354649090586</v>
+        <v>0.1063003798369794</v>
       </c>
       <c r="C36">
-        <v>65.00872262939268</v>
+        <v>64.63749674888847</v>
       </c>
       <c r="D36">
-        <v>88.21472262939268</v>
+        <v>88.55749674888848</v>
       </c>
       <c r="E36">
-        <v>-19.42400000000001</v>
+        <v>-18.71</v>
       </c>
       <c r="F36">
-        <v>24.276</v>
+        <v>24.99000000000001</v>
       </c>
       <c r="G36">
         <v>1.07</v>
@@ -4239,28 +4239,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M36">
-        <v>1.4881188</v>
+        <v>1.531887</v>
       </c>
       <c r="N36">
-        <v>4.098547866666667</v>
+        <v>4.054779666666668</v>
       </c>
       <c r="O36">
-        <v>1.22956436</v>
+        <v>1.2164339</v>
       </c>
       <c r="P36">
-        <v>2.868983506666667</v>
+        <v>2.838345766666667</v>
       </c>
       <c r="Q36">
-        <v>3.198983506666667</v>
+        <v>3.168345766666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1393122195591798</v>
+        <v>0.1404336612876606</v>
       </c>
       <c r="T36">
-        <v>0.8010054485602073</v>
+        <v>0.8106114758686216</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.75418055780672</v>
+        <v>3.646918256155099</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1063003798369794</v>
+        <v>0.1060652947649001</v>
       </c>
       <c r="C37">
-        <v>64.63749674888847</v>
+        <v>64.26894508009777</v>
       </c>
       <c r="D37">
-        <v>88.55749674888848</v>
+        <v>88.90294508009778</v>
       </c>
       <c r="E37">
-        <v>-18.71</v>
+        <v>-17.99600000000001</v>
       </c>
       <c r="F37">
-        <v>24.99000000000001</v>
+        <v>25.704</v>
       </c>
       <c r="G37">
         <v>1.07</v>
@@ -4321,28 +4321,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M37">
-        <v>1.531887</v>
+        <v>1.5756552</v>
       </c>
       <c r="N37">
-        <v>4.054779666666668</v>
+        <v>4.011011466666668</v>
       </c>
       <c r="O37">
-        <v>1.2164339</v>
+        <v>1.20330344</v>
       </c>
       <c r="P37">
-        <v>2.838345766666667</v>
+        <v>2.807708026666668</v>
       </c>
       <c r="Q37">
-        <v>3.168345766666667</v>
+        <v>3.137708026666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1404336612876606</v>
+        <v>0.1415901480701565</v>
       </c>
       <c r="T37">
-        <v>0.8106114758686216</v>
+        <v>0.820517691530424</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.646918256155099</v>
+        <v>3.545614971261903</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1060652947649001</v>
+        <v>0.1065554096928209</v>
       </c>
       <c r="C38">
-        <v>64.26894508009775</v>
+        <v>62.8377635033431</v>
       </c>
       <c r="D38">
-        <v>88.90294508009777</v>
+        <v>88.18576350334311</v>
       </c>
       <c r="E38">
-        <v>-17.99600000000001</v>
+        <v>-17.28200000000001</v>
       </c>
       <c r="F38">
-        <v>25.704</v>
+        <v>26.418</v>
       </c>
       <c r="G38">
         <v>1.07</v>
@@ -4403,45 +4403,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M38">
-        <v>1.5756552</v>
+        <v>1.6933938</v>
       </c>
       <c r="N38">
-        <v>4.011011466666668</v>
+        <v>3.893272866666667</v>
       </c>
       <c r="O38">
-        <v>1.20330344</v>
+        <v>1.16798186</v>
       </c>
       <c r="P38">
-        <v>2.807708026666668</v>
+        <v>2.725291006666667</v>
       </c>
       <c r="Q38">
-        <v>3.137708026666667</v>
+        <v>3.055291006666667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1415901480701565</v>
+        <v>0.1427833487187633</v>
       </c>
       <c r="T38">
-        <v>0.820517691530424</v>
+        <v>0.8307383902291088</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.545614971261903</v>
+        <v>3.299094792166279</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1065554096928209</v>
+        <v>0.1063399246207416</v>
       </c>
       <c r="C39">
-        <v>62.8377635033431</v>
+        <v>62.4376508384187</v>
       </c>
       <c r="D39">
-        <v>88.18576350334311</v>
+        <v>88.49965083841872</v>
       </c>
       <c r="E39">
-        <v>-17.28200000000001</v>
+        <v>-16.56800000000001</v>
       </c>
       <c r="F39">
-        <v>26.418</v>
+        <v>27.132</v>
       </c>
       <c r="G39">
         <v>1.07</v>
@@ -4485,28 +4485,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M39">
-        <v>1.6933938</v>
+        <v>1.7391612</v>
       </c>
       <c r="N39">
-        <v>3.893272866666667</v>
+        <v>3.847505466666667</v>
       </c>
       <c r="O39">
-        <v>1.16798186</v>
+        <v>1.15425164</v>
       </c>
       <c r="P39">
-        <v>2.725291006666667</v>
+        <v>2.693253826666667</v>
       </c>
       <c r="Q39">
-        <v>3.055291006666667</v>
+        <v>3.023253826666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1427833487187633</v>
+        <v>0.1440150397108736</v>
       </c>
       <c r="T39">
-        <v>0.8307383902291088</v>
+        <v>0.8412887888858158</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.299094792166279</v>
+        <v>3.212276508161904</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1063399246207416</v>
+        <v>0.1061244395486624</v>
       </c>
       <c r="C40">
-        <v>62.4376508384187</v>
+        <v>62.0397806488668</v>
       </c>
       <c r="D40">
-        <v>88.49965083841872</v>
+        <v>88.81578064886681</v>
       </c>
       <c r="E40">
-        <v>-16.56800000000001</v>
+        <v>-15.85400000000001</v>
       </c>
       <c r="F40">
-        <v>27.132</v>
+        <v>27.846</v>
       </c>
       <c r="G40">
         <v>1.07</v>
@@ -4567,28 +4567,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M40">
-        <v>1.7391612</v>
+        <v>1.7849286</v>
       </c>
       <c r="N40">
-        <v>3.847505466666667</v>
+        <v>3.801738066666667</v>
       </c>
       <c r="O40">
-        <v>1.15425164</v>
+        <v>1.14052142</v>
       </c>
       <c r="P40">
-        <v>2.693253826666667</v>
+        <v>2.661216646666667</v>
       </c>
       <c r="Q40">
-        <v>3.023253826666667</v>
+        <v>2.991216646666667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1440150397108736</v>
+        <v>0.1452871140142006</v>
       </c>
       <c r="T40">
-        <v>0.8412887888858158</v>
+        <v>0.8521851022525788</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.212276508161904</v>
+        <v>3.12991044385006</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1061244395486624</v>
+        <v>0.1059089544765831</v>
       </c>
       <c r="C41">
-        <v>62.0397806488668</v>
+        <v>61.64417705189112</v>
       </c>
       <c r="D41">
-        <v>88.81578064886681</v>
+        <v>89.13417705189113</v>
       </c>
       <c r="E41">
-        <v>-15.85400000000001</v>
+        <v>-15.14000000000001</v>
       </c>
       <c r="F41">
-        <v>27.846</v>
+        <v>28.56</v>
       </c>
       <c r="G41">
         <v>1.07</v>
@@ -4649,28 +4649,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M41">
-        <v>1.7849286</v>
+        <v>1.830696</v>
       </c>
       <c r="N41">
-        <v>3.801738066666667</v>
+        <v>3.755970666666667</v>
       </c>
       <c r="O41">
-        <v>1.14052142</v>
+        <v>1.1267912</v>
       </c>
       <c r="P41">
-        <v>2.661216646666667</v>
+        <v>2.629179466666667</v>
       </c>
       <c r="Q41">
-        <v>2.991216646666667</v>
+        <v>2.959179466666666</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1452871140142006</v>
+        <v>0.1466015907943052</v>
       </c>
       <c r="T41">
-        <v>0.8521851022525788</v>
+        <v>0.8634446260649006</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.12991044385006</v>
+        <v>3.051662682753809</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1059089544765831</v>
+        <v>0.1079320694045038</v>
       </c>
       <c r="C42">
-        <v>61.64417705189112</v>
+        <v>58.02783232218958</v>
       </c>
       <c r="D42">
-        <v>89.13417705189113</v>
+        <v>86.23183232218959</v>
       </c>
       <c r="E42">
-        <v>-15.14000000000001</v>
+        <v>-14.42600000000001</v>
       </c>
       <c r="F42">
-        <v>28.56</v>
+        <v>29.274</v>
       </c>
       <c r="G42">
         <v>1.07</v>
@@ -4731,45 +4731,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M42">
-        <v>1.830696</v>
+        <v>2.1048006</v>
       </c>
       <c r="N42">
-        <v>3.755970666666667</v>
+        <v>3.481866066666667</v>
       </c>
       <c r="O42">
-        <v>1.1267912</v>
+        <v>1.04455982</v>
       </c>
       <c r="P42">
-        <v>2.629179466666667</v>
+        <v>2.437306246666667</v>
       </c>
       <c r="Q42">
-        <v>2.959179466666666</v>
+        <v>2.767306246666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1466015907943052</v>
+        <v>0.1479606261093285</v>
       </c>
       <c r="T42">
-        <v>0.8634446260649006</v>
+        <v>0.8750858286505213</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.051662682753809</v>
+        <v>2.654249845171399</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1079320694045038</v>
+        <v>0.1077711843324246</v>
       </c>
       <c r="C43">
-        <v>58.02783232218958</v>
+        <v>57.53770112037592</v>
       </c>
       <c r="D43">
-        <v>86.23183232218959</v>
+        <v>86.45570112037593</v>
       </c>
       <c r="E43">
-        <v>-14.42600000000001</v>
+        <v>-13.712</v>
       </c>
       <c r="F43">
-        <v>29.274</v>
+        <v>29.98800000000001</v>
       </c>
       <c r="G43">
         <v>1.07</v>
@@ -4813,28 +4813,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M43">
-        <v>2.1048006</v>
+        <v>2.156137200000001</v>
       </c>
       <c r="N43">
-        <v>3.481866066666667</v>
+        <v>3.430529466666667</v>
       </c>
       <c r="O43">
-        <v>1.04455982</v>
+        <v>1.02915884</v>
       </c>
       <c r="P43">
-        <v>2.437306246666667</v>
+        <v>2.401370626666667</v>
       </c>
       <c r="Q43">
-        <v>2.767306246666667</v>
+        <v>2.731370626666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1479606261093285</v>
+        <v>0.1493665247110768</v>
       </c>
       <c r="T43">
-        <v>0.8750858286505213</v>
+        <v>0.8871284520149566</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.654249845171399</v>
+        <v>2.591053420286365</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1077711843324246</v>
+        <v>0.1076102992603453</v>
       </c>
       <c r="C44">
-        <v>57.53770112037589</v>
+        <v>57.0487353278278</v>
       </c>
       <c r="D44">
-        <v>86.45570112037589</v>
+        <v>86.6807353278278</v>
       </c>
       <c r="E44">
-        <v>-13.71200000000001</v>
+        <v>-12.99800000000001</v>
       </c>
       <c r="F44">
-        <v>29.988</v>
+        <v>30.702</v>
       </c>
       <c r="G44">
         <v>1.07</v>
@@ -4895,28 +4895,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M44">
-        <v>2.1561372</v>
+        <v>2.2074738</v>
       </c>
       <c r="N44">
-        <v>3.430529466666667</v>
+        <v>3.379192866666668</v>
       </c>
       <c r="O44">
-        <v>1.02915884</v>
+        <v>1.01375786</v>
       </c>
       <c r="P44">
-        <v>2.401370626666667</v>
+        <v>2.365435006666667</v>
       </c>
       <c r="Q44">
-        <v>2.731370626666667</v>
+        <v>2.695435006666667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1493665247110768</v>
+        <v>0.1508217530883251</v>
       </c>
       <c r="T44">
-        <v>0.8871284520149565</v>
+        <v>0.8995936235676175</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.591053420286365</v>
+        <v>2.530796364000636</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1076102992603453</v>
+        <v>0.108650614188266</v>
       </c>
       <c r="C45">
-        <v>57.0487353278278</v>
+        <v>54.89997985106235</v>
       </c>
       <c r="D45">
-        <v>86.6807353278278</v>
+        <v>85.24597985106236</v>
       </c>
       <c r="E45">
-        <v>-12.99800000000001</v>
+        <v>-12.28400000000001</v>
       </c>
       <c r="F45">
-        <v>30.702</v>
+        <v>31.416</v>
       </c>
       <c r="G45">
         <v>1.07</v>
@@ -4977,45 +4977,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M45">
-        <v>2.2074738</v>
+        <v>2.3813328</v>
       </c>
       <c r="N45">
-        <v>3.379192866666668</v>
+        <v>3.205333866666667</v>
       </c>
       <c r="O45">
-        <v>1.01375786</v>
+        <v>0.9616001600000001</v>
       </c>
       <c r="P45">
-        <v>2.365435006666667</v>
+        <v>2.243733706666667</v>
       </c>
       <c r="Q45">
-        <v>2.695435006666667</v>
+        <v>2.573733706666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1508217530883251</v>
+        <v>0.1523289539076179</v>
       </c>
       <c r="T45">
-        <v>0.8995936235676175</v>
+        <v>0.9125039798185879</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.530796364000636</v>
+        <v>2.346025161483799</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.108650614188266</v>
+        <v>0.1085170291161868</v>
       </c>
       <c r="C46">
-        <v>54.89997985106235</v>
+        <v>54.3675507979542</v>
       </c>
       <c r="D46">
-        <v>85.24597985106236</v>
+        <v>85.42755079795421</v>
       </c>
       <c r="E46">
-        <v>-12.28400000000001</v>
+        <v>-11.57000000000001</v>
       </c>
       <c r="F46">
-        <v>31.416</v>
+        <v>32.13</v>
       </c>
       <c r="G46">
         <v>1.07</v>
@@ -5059,28 +5059,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M46">
-        <v>2.3813328</v>
+        <v>2.435454</v>
       </c>
       <c r="N46">
-        <v>3.205333866666667</v>
+        <v>3.151212666666667</v>
       </c>
       <c r="O46">
-        <v>0.9616001600000001</v>
+        <v>0.9453638000000002</v>
       </c>
       <c r="P46">
-        <v>2.243733706666667</v>
+        <v>2.205848866666667</v>
       </c>
       <c r="Q46">
-        <v>2.573733706666667</v>
+        <v>2.535848866666667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1523289539076179</v>
+        <v>0.1538909620294305</v>
       </c>
       <c r="T46">
-        <v>0.9125039798185879</v>
+        <v>0.9258838035695938</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.346025161483799</v>
+        <v>2.293891269006381</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1085170291161868</v>
+        <v>0.1083834440441075</v>
       </c>
       <c r="C47">
-        <v>54.3675507979542</v>
+        <v>53.83589687534261</v>
       </c>
       <c r="D47">
-        <v>85.42755079795421</v>
+        <v>85.60989687534261</v>
       </c>
       <c r="E47">
-        <v>-11.57000000000001</v>
+        <v>-10.85600000000001</v>
       </c>
       <c r="F47">
-        <v>32.13</v>
+        <v>32.844</v>
       </c>
       <c r="G47">
         <v>1.07</v>
@@ -5141,28 +5141,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M47">
-        <v>2.435454</v>
+        <v>2.4895752</v>
       </c>
       <c r="N47">
-        <v>3.151212666666667</v>
+        <v>3.097091466666667</v>
       </c>
       <c r="O47">
-        <v>0.9453638000000002</v>
+        <v>0.9291274400000001</v>
       </c>
       <c r="P47">
-        <v>2.205848866666667</v>
+        <v>2.167964026666667</v>
       </c>
       <c r="Q47">
-        <v>2.535848866666667</v>
+        <v>2.497964026666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1538909620294305</v>
+        <v>0.1555108223039028</v>
       </c>
       <c r="T47">
-        <v>0.9258838035695938</v>
+        <v>0.9397591763484143</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.293891269006381</v>
+        <v>2.244024067506242</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1083834440441075</v>
+        <v>0.1082498589720283</v>
       </c>
       <c r="C48">
-        <v>53.83589687534261</v>
+        <v>53.30502305741952</v>
       </c>
       <c r="D48">
-        <v>85.60989687534261</v>
+        <v>85.79302305741953</v>
       </c>
       <c r="E48">
-        <v>-10.85600000000001</v>
+        <v>-10.142</v>
       </c>
       <c r="F48">
-        <v>32.844</v>
+        <v>33.55800000000001</v>
       </c>
       <c r="G48">
         <v>1.07</v>
@@ -5223,28 +5223,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M48">
-        <v>2.4895752</v>
+        <v>2.543696400000001</v>
       </c>
       <c r="N48">
-        <v>3.097091466666667</v>
+        <v>3.042970266666667</v>
       </c>
       <c r="O48">
-        <v>0.9291274400000001</v>
+        <v>0.9128910800000001</v>
       </c>
       <c r="P48">
-        <v>2.167964026666667</v>
+        <v>2.130079186666667</v>
       </c>
       <c r="Q48">
-        <v>2.497964026666667</v>
+        <v>2.460079186666666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1555108223039028</v>
+        <v>0.1571918093811854</v>
       </c>
       <c r="T48">
-        <v>0.9397591763484143</v>
+        <v>0.9541581481000209</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.244024067506242</v>
+        <v>2.196278874580577</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1082498589720283</v>
+        <v>0.108116273899949</v>
       </c>
       <c r="C49">
-        <v>53.30502305741952</v>
+        <v>52.77493436102901</v>
       </c>
       <c r="D49">
-        <v>85.79302305741953</v>
+        <v>85.97693436102902</v>
       </c>
       <c r="E49">
-        <v>-10.142</v>
+        <v>-9.428000000000004</v>
       </c>
       <c r="F49">
-        <v>33.55800000000001</v>
+        <v>34.27200000000001</v>
       </c>
       <c r="G49">
         <v>1.07</v>
@@ -5305,28 +5305,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M49">
-        <v>2.543696400000001</v>
+        <v>2.597817600000001</v>
       </c>
       <c r="N49">
-        <v>3.042970266666667</v>
+        <v>2.988849066666667</v>
       </c>
       <c r="O49">
-        <v>0.9128910800000001</v>
+        <v>0.89665472</v>
       </c>
       <c r="P49">
-        <v>2.130079186666667</v>
+        <v>2.092194346666667</v>
       </c>
       <c r="Q49">
-        <v>2.460079186666666</v>
+        <v>2.422194346666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1571918093811854</v>
+        <v>0.1589374498075942</v>
       </c>
       <c r="T49">
-        <v>0.9541581481000209</v>
+        <v>0.9691109264574582</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.196278874580577</v>
+        <v>2.150523064693482</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.108116273899949</v>
+        <v>0.1079826888278697</v>
       </c>
       <c r="C50">
-        <v>52.77493436102902</v>
+        <v>52.24563584612504</v>
       </c>
       <c r="D50">
-        <v>85.97693436102902</v>
+        <v>86.16163584612505</v>
       </c>
       <c r="E50">
-        <v>-9.428000000000011</v>
+        <v>-8.714000000000006</v>
       </c>
       <c r="F50">
-        <v>34.272</v>
+        <v>34.986</v>
       </c>
       <c r="G50">
         <v>1.07</v>
@@ -5387,28 +5387,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M50">
-        <v>2.5978176</v>
+        <v>2.6519388</v>
       </c>
       <c r="N50">
-        <v>2.988849066666668</v>
+        <v>2.934727866666667</v>
       </c>
       <c r="O50">
-        <v>0.8966547200000003</v>
+        <v>0.8804183600000002</v>
       </c>
       <c r="P50">
-        <v>2.092194346666667</v>
+        <v>2.054309506666667</v>
       </c>
       <c r="Q50">
-        <v>2.422194346666667</v>
+        <v>2.384309506666667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1589374498075942</v>
+        <v>0.1607515467213132</v>
       </c>
       <c r="T50">
-        <v>0.9691109264574582</v>
+        <v>0.9846500882798931</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.150523064693483</v>
+        <v>2.106634838883411</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1079826888278697</v>
+        <v>0.1078491037557905</v>
       </c>
       <c r="C51">
-        <v>52.24563584612504</v>
+        <v>51.71713261623587</v>
       </c>
       <c r="D51">
-        <v>86.16163584612505</v>
+        <v>86.34713261623588</v>
       </c>
       <c r="E51">
-        <v>-8.714000000000006</v>
+        <v>-8.000000000000007</v>
       </c>
       <c r="F51">
-        <v>34.986</v>
+        <v>35.7</v>
       </c>
       <c r="G51">
         <v>1.07</v>
@@ -5469,28 +5469,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M51">
-        <v>2.6519388</v>
+        <v>2.70606</v>
       </c>
       <c r="N51">
-        <v>2.934727866666667</v>
+        <v>2.880606666666667</v>
       </c>
       <c r="O51">
-        <v>0.8804183600000002</v>
+        <v>0.8641820000000002</v>
       </c>
       <c r="P51">
-        <v>2.054309506666667</v>
+        <v>2.016424666666667</v>
       </c>
       <c r="Q51">
-        <v>2.384309506666667</v>
+        <v>2.346424666666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1607515467213132</v>
+        <v>0.162638207511581</v>
       </c>
       <c r="T51">
-        <v>0.9846500882798931</v>
+        <v>1.000810816575226</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.106634838883411</v>
+        <v>2.064502142105743</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1078491037557905</v>
+        <v>0.1077155186837112</v>
       </c>
       <c r="C52">
-        <v>51.71713261623587</v>
+        <v>51.18942981893397</v>
       </c>
       <c r="D52">
-        <v>86.34713261623588</v>
+        <v>86.53342981893398</v>
       </c>
       <c r="E52">
-        <v>-8.000000000000007</v>
+        <v>-7.286000000000008</v>
       </c>
       <c r="F52">
-        <v>35.7</v>
+        <v>36.414</v>
       </c>
       <c r="G52">
         <v>1.07</v>
@@ -5551,28 +5551,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M52">
-        <v>2.70606</v>
+        <v>2.7601812</v>
       </c>
       <c r="N52">
-        <v>2.880606666666667</v>
+        <v>2.826485466666667</v>
       </c>
       <c r="O52">
-        <v>0.8641820000000002</v>
+        <v>0.8479456400000002</v>
       </c>
       <c r="P52">
-        <v>2.016424666666667</v>
+        <v>1.978539826666667</v>
       </c>
       <c r="Q52">
-        <v>2.346424666666667</v>
+        <v>2.308539826666667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.162638207511581</v>
+        <v>0.1646018748647168</v>
       </c>
       <c r="T52">
-        <v>1.000810816575226</v>
+        <v>1.017631166433633</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.064502142105743</v>
+        <v>2.024021707946807</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1077155186837112</v>
+        <v>0.112750733611632</v>
       </c>
       <c r="C53">
-        <v>51.18942981893397</v>
+        <v>43.96744410938265</v>
       </c>
       <c r="D53">
-        <v>86.53342981893398</v>
+        <v>80.02544410938266</v>
       </c>
       <c r="E53">
-        <v>-7.286000000000008</v>
+        <v>-6.572000000000003</v>
       </c>
       <c r="F53">
-        <v>36.414</v>
+        <v>37.12800000000001</v>
       </c>
       <c r="G53">
         <v>1.07</v>
@@ -5633,45 +5633,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M53">
-        <v>2.7601812</v>
+        <v>3.34152</v>
       </c>
       <c r="N53">
-        <v>2.826485466666667</v>
+        <v>2.245146666666667</v>
       </c>
       <c r="O53">
-        <v>0.8479456400000002</v>
+        <v>0.6735440000000001</v>
       </c>
       <c r="P53">
-        <v>1.978539826666667</v>
+        <v>1.571602666666667</v>
       </c>
       <c r="Q53">
-        <v>2.308539826666667</v>
+        <v>1.901602666666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1646018748647168</v>
+        <v>0.1666473616908999</v>
       </c>
       <c r="T53">
-        <v>1.017631166433633</v>
+        <v>1.035152364202807</v>
       </c>
       <c r="U53">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.024021707946807</v>
+        <v>1.671893828756574</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.112750733611632</v>
+        <v>0.1127165485395527</v>
       </c>
       <c r="C54">
-        <v>43.96744410938265</v>
+        <v>43.29432600832633</v>
       </c>
       <c r="D54">
-        <v>80.02544410938266</v>
+        <v>80.06632600832634</v>
       </c>
       <c r="E54">
-        <v>-6.572000000000003</v>
+        <v>-5.858000000000004</v>
       </c>
       <c r="F54">
-        <v>37.12800000000001</v>
+        <v>37.84200000000001</v>
       </c>
       <c r="G54">
         <v>1.07</v>
@@ -5715,28 +5715,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M54">
-        <v>3.34152</v>
+        <v>3.40578</v>
       </c>
       <c r="N54">
-        <v>2.245146666666667</v>
+        <v>2.180886666666667</v>
       </c>
       <c r="O54">
-        <v>0.6735440000000001</v>
+        <v>0.6542660000000001</v>
       </c>
       <c r="P54">
-        <v>1.571602666666667</v>
+        <v>1.526620666666667</v>
       </c>
       <c r="Q54">
-        <v>1.901602666666667</v>
+        <v>1.856620666666667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1666473616908999</v>
+        <v>0.1687798905096866</v>
       </c>
       <c r="T54">
-        <v>1.035152364202807</v>
+        <v>1.053419144855776</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.671893828756574</v>
+        <v>1.640348662176261</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1127165485395527</v>
+        <v>0.1126823634674734</v>
       </c>
       <c r="C55">
-        <v>43.29432600832633</v>
+        <v>42.62124969857613</v>
       </c>
       <c r="D55">
-        <v>80.06632600832634</v>
+        <v>80.10724969857614</v>
       </c>
       <c r="E55">
-        <v>-5.858000000000004</v>
+        <v>-5.144000000000005</v>
       </c>
       <c r="F55">
-        <v>37.84200000000001</v>
+        <v>38.556</v>
       </c>
       <c r="G55">
         <v>1.07</v>
@@ -5797,28 +5797,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M55">
-        <v>3.40578</v>
+        <v>3.47004</v>
       </c>
       <c r="N55">
-        <v>2.180886666666667</v>
+        <v>2.116626666666667</v>
       </c>
       <c r="O55">
-        <v>0.6542660000000001</v>
+        <v>0.6349880000000002</v>
       </c>
       <c r="P55">
-        <v>1.526620666666667</v>
+        <v>1.481638666666667</v>
       </c>
       <c r="Q55">
-        <v>1.856620666666667</v>
+        <v>1.811638666666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1687798905096866</v>
+        <v>0.1710051379727683</v>
       </c>
       <c r="T55">
-        <v>1.053419144855776</v>
+        <v>1.072480133363221</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.640348662176261</v>
+        <v>1.609971835098923</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1126823634674734</v>
+        <v>0.1126481783953942</v>
       </c>
       <c r="C56">
-        <v>42.62124969857613</v>
+        <v>41.94821524424619</v>
       </c>
       <c r="D56">
-        <v>80.10724969857614</v>
+        <v>80.1482152442462</v>
       </c>
       <c r="E56">
-        <v>-5.144000000000005</v>
+        <v>-4.430000000000007</v>
       </c>
       <c r="F56">
-        <v>38.556</v>
+        <v>39.27</v>
       </c>
       <c r="G56">
         <v>1.07</v>
@@ -5879,28 +5879,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M56">
-        <v>3.47004</v>
+        <v>3.5343</v>
       </c>
       <c r="N56">
-        <v>2.116626666666667</v>
+        <v>2.052366666666668</v>
       </c>
       <c r="O56">
-        <v>0.6349880000000002</v>
+        <v>0.6157100000000003</v>
       </c>
       <c r="P56">
-        <v>1.481638666666667</v>
+        <v>1.436656666666667</v>
       </c>
       <c r="Q56">
-        <v>1.811638666666667</v>
+        <v>1.766656666666667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1710051379727683</v>
+        <v>0.1733292853230982</v>
       </c>
       <c r="T56">
-        <v>1.072480133363221</v>
+        <v>1.092388276915442</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.609971835098923</v>
+        <v>1.580699619915306</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1126481783953942</v>
+        <v>0.1126139933233149</v>
       </c>
       <c r="C57">
-        <v>41.94821524424619</v>
+        <v>41.27522270958191</v>
       </c>
       <c r="D57">
-        <v>80.1482152442462</v>
+        <v>80.18922270958193</v>
       </c>
       <c r="E57">
-        <v>-4.430000000000007</v>
+        <v>-3.716000000000001</v>
       </c>
       <c r="F57">
-        <v>39.27</v>
+        <v>39.98400000000001</v>
       </c>
       <c r="G57">
         <v>1.07</v>
@@ -5961,28 +5961,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M57">
-        <v>3.5343</v>
+        <v>3.598560000000001</v>
       </c>
       <c r="N57">
-        <v>2.052366666666668</v>
+        <v>1.988106666666667</v>
       </c>
       <c r="O57">
-        <v>0.6157100000000003</v>
+        <v>0.5964320000000001</v>
       </c>
       <c r="P57">
-        <v>1.436656666666667</v>
+        <v>1.391674666666667</v>
       </c>
       <c r="Q57">
-        <v>1.766656666666667</v>
+        <v>1.721674666666666</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1733292853230982</v>
+        <v>0.1757590757348066</v>
       </c>
       <c r="T57">
-        <v>1.092388276915442</v>
+        <v>1.113201336083673</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.580699619915306</v>
+        <v>1.552472840988247</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1126139933233149</v>
+        <v>0.1125798082512356</v>
       </c>
       <c r="C58">
-        <v>41.27522270958191</v>
+        <v>40.60227215896032</v>
       </c>
       <c r="D58">
-        <v>80.18922270958193</v>
+        <v>80.23027215896033</v>
       </c>
       <c r="E58">
-        <v>-3.716000000000001</v>
+        <v>-3.002000000000002</v>
       </c>
       <c r="F58">
-        <v>39.98400000000001</v>
+        <v>40.69800000000001</v>
       </c>
       <c r="G58">
         <v>1.07</v>
@@ -6043,28 +6043,28 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M58">
-        <v>3.598560000000001</v>
+        <v>3.66282</v>
       </c>
       <c r="N58">
-        <v>1.988106666666667</v>
+        <v>1.923846666666667</v>
       </c>
       <c r="O58">
-        <v>0.5964320000000001</v>
+        <v>0.5771540000000002</v>
       </c>
       <c r="P58">
-        <v>1.391674666666667</v>
+        <v>1.346692666666667</v>
       </c>
       <c r="Q58">
-        <v>1.721674666666666</v>
+        <v>1.676692666666667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1757590757348066</v>
+        <v>0.1783018796540364</v>
       </c>
       <c r="T58">
-        <v>1.113201336083673</v>
+        <v>1.134982444515543</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.552472840988247</v>
+        <v>1.525236475356875</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1125798082512356</v>
+        <v>0.1386452711914357</v>
       </c>
       <c r="C59">
-        <v>40.60227215896032</v>
+        <v>17.36435512144464</v>
       </c>
       <c r="D59">
-        <v>80.23027215896033</v>
+        <v>57.70635512144464</v>
       </c>
       <c r="E59">
-        <v>-3.002000000000002</v>
+        <v>-2.288000000000004</v>
       </c>
       <c r="F59">
-        <v>40.69800000000001</v>
+        <v>41.41200000000001</v>
       </c>
       <c r="G59">
         <v>1.07</v>
@@ -6125,45 +6125,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M59">
-        <v>3.66282</v>
+        <v>6.079281600000002</v>
       </c>
       <c r="N59">
-        <v>1.923846666666667</v>
+        <v>-0.4926149333333338</v>
       </c>
       <c r="O59">
-        <v>0.5771540000000002</v>
+        <v>-0.1477844800000001</v>
       </c>
       <c r="P59">
-        <v>1.346692666666667</v>
+        <v>-0.3448304533333337</v>
       </c>
       <c r="Q59">
-        <v>1.676692666666667</v>
+        <v>-0.0148304533333341</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1783018796540364</v>
+        <v>0.1832730013028047</v>
       </c>
       <c r="T59">
-        <v>1.134982444515543</v>
+        <v>1.177563997438678</v>
       </c>
       <c r="U59">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.3</v>
+        <v>0.2756904697423458</v>
       </c>
       <c r="W59">
-        <v>0.063</v>
+        <v>0.1063286390418236</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.525236475356875</v>
+        <v>0.9189682324744862</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1386452711914357</v>
+        <v>0.1396552711914357</v>
       </c>
       <c r="C60">
-        <v>17.36435512144465</v>
+        <v>16.02936263021014</v>
       </c>
       <c r="D60">
-        <v>57.70635512144464</v>
+        <v>57.08536263021014</v>
       </c>
       <c r="E60">
-        <v>-2.288000000000011</v>
+        <v>-1.574000000000012</v>
       </c>
       <c r="F60">
-        <v>41.412</v>
+        <v>42.126</v>
       </c>
       <c r="G60">
         <v>1.07</v>
@@ -6207,37 +6207,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M60">
-        <v>6.079281600000001</v>
+        <v>6.1840968</v>
       </c>
       <c r="N60">
-        <v>-0.4926149333333329</v>
+        <v>-0.5974301333333321</v>
       </c>
       <c r="O60">
-        <v>-0.1477844799999999</v>
+        <v>-0.1792290399999996</v>
       </c>
       <c r="P60">
-        <v>-0.3448304533333331</v>
+        <v>-0.4182010933333324</v>
       </c>
       <c r="Q60">
-        <v>-0.01483045333333344</v>
+        <v>-0.08820109333333281</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1832730013028047</v>
+        <v>0.1866260013345804</v>
       </c>
       <c r="T60">
-        <v>1.177563997438677</v>
+        <v>1.206285070546938</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2756904697423459</v>
+        <v>0.2710177499162045</v>
       </c>
       <c r="W60">
-        <v>0.1063286390418236</v>
+        <v>0.1070145943123012</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9189682324744863</v>
+        <v>0.9033924997206816</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1396552711914357</v>
+        <v>0.1406652711914357</v>
       </c>
       <c r="C61">
-        <v>16.02936263021014</v>
+        <v>14.70759315322038</v>
       </c>
       <c r="D61">
-        <v>57.08536263021014</v>
+        <v>56.47759315322038</v>
       </c>
       <c r="E61">
-        <v>-1.574000000000012</v>
+        <v>-0.8600000000000065</v>
       </c>
       <c r="F61">
-        <v>42.126</v>
+        <v>42.84</v>
       </c>
       <c r="G61">
         <v>1.07</v>
@@ -6289,37 +6289,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M61">
-        <v>6.1840968</v>
+        <v>6.288912000000001</v>
       </c>
       <c r="N61">
-        <v>-0.5974301333333321</v>
+        <v>-0.7022453333333329</v>
       </c>
       <c r="O61">
-        <v>-0.1792290399999996</v>
+        <v>-0.2106735999999999</v>
       </c>
       <c r="P61">
-        <v>-0.4182010933333324</v>
+        <v>-0.491571733333333</v>
       </c>
       <c r="Q61">
-        <v>-0.08820109333333281</v>
+        <v>-0.1615717333333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1866260013345804</v>
+        <v>0.1901466513679449</v>
       </c>
       <c r="T61">
-        <v>1.206285070546938</v>
+        <v>1.236442197310611</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2710177499162045</v>
+        <v>0.266500787417601</v>
       </c>
       <c r="W61">
-        <v>0.1070145943123012</v>
+        <v>0.1076776844070962</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9033924997206816</v>
+        <v>0.88833595805867</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1406652711914357</v>
+        <v>0.1416752711914357</v>
       </c>
       <c r="C62">
-        <v>14.70759315322038</v>
+        <v>13.39862879613548</v>
       </c>
       <c r="D62">
-        <v>56.47759315322038</v>
+        <v>55.88262879613548</v>
       </c>
       <c r="E62">
-        <v>-0.8600000000000065</v>
+        <v>-0.1460000000000079</v>
       </c>
       <c r="F62">
-        <v>42.84</v>
+        <v>43.554</v>
       </c>
       <c r="G62">
         <v>1.07</v>
@@ -6371,37 +6371,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M62">
-        <v>6.288912000000001</v>
+        <v>6.393727200000001</v>
       </c>
       <c r="N62">
-        <v>-0.7022453333333329</v>
+        <v>-0.8070605333333329</v>
       </c>
       <c r="O62">
-        <v>-0.2106735999999999</v>
+        <v>-0.2421181599999999</v>
       </c>
       <c r="P62">
-        <v>-0.491571733333333</v>
+        <v>-0.5649423733333331</v>
       </c>
       <c r="Q62">
-        <v>-0.1615717333333334</v>
+        <v>-0.2349423733333335</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1901466513679449</v>
+        <v>0.1938478475568665</v>
       </c>
       <c r="T62">
-        <v>1.236442197310611</v>
+        <v>1.268145843395499</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.266500787417601</v>
+        <v>0.2621319220500994</v>
       </c>
       <c r="W62">
-        <v>0.1076776844070962</v>
+        <v>0.1083190338430454</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.88833595805867</v>
+        <v>0.8737730735003313</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1416752711914357</v>
+        <v>0.1426852711914357</v>
       </c>
       <c r="C63">
-        <v>13.39862879613548</v>
+        <v>12.10206909031007</v>
       </c>
       <c r="D63">
-        <v>55.88262879613548</v>
+        <v>55.30006909031007</v>
       </c>
       <c r="E63">
-        <v>-0.1460000000000079</v>
+        <v>0.5679999999999907</v>
       </c>
       <c r="F63">
-        <v>43.554</v>
+        <v>44.268</v>
       </c>
       <c r="G63">
         <v>1.07</v>
@@ -6453,37 +6453,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M63">
-        <v>6.393727200000001</v>
+        <v>6.498542400000001</v>
       </c>
       <c r="N63">
-        <v>-0.8070605333333329</v>
+        <v>-0.9118757333333329</v>
       </c>
       <c r="O63">
-        <v>-0.2421181599999999</v>
+        <v>-0.2735627199999999</v>
       </c>
       <c r="P63">
-        <v>-0.5649423733333331</v>
+        <v>-0.638313013333333</v>
       </c>
       <c r="Q63">
-        <v>-0.2349423733333335</v>
+        <v>-0.3083130133333334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1938478475568665</v>
+        <v>0.1977438435452052</v>
       </c>
       <c r="T63">
-        <v>1.268145843395499</v>
+        <v>1.301518102432222</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2621319220500994</v>
+        <v>0.2579039878234848</v>
       </c>
       <c r="W63">
-        <v>0.1083190338430454</v>
+        <v>0.1089396945875124</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8737730735003313</v>
+        <v>0.8596799594116162</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1426852711914357</v>
+        <v>0.1436952711914357</v>
       </c>
       <c r="C64">
-        <v>12.10206909031007</v>
+        <v>10.8175300938759</v>
       </c>
       <c r="D64">
-        <v>55.30006909031007</v>
+        <v>54.7295300938759</v>
       </c>
       <c r="E64">
-        <v>0.5679999999999907</v>
+        <v>1.281999999999996</v>
       </c>
       <c r="F64">
-        <v>44.268</v>
+        <v>44.98200000000001</v>
       </c>
       <c r="G64">
         <v>1.07</v>
@@ -6535,37 +6535,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M64">
-        <v>6.498542400000001</v>
+        <v>6.603357600000002</v>
       </c>
       <c r="N64">
-        <v>-0.9118757333333329</v>
+        <v>-1.016690933333334</v>
       </c>
       <c r="O64">
-        <v>-0.2735627199999999</v>
+        <v>-0.3050072800000002</v>
       </c>
       <c r="P64">
-        <v>-0.638313013333333</v>
+        <v>-0.7116836533333337</v>
       </c>
       <c r="Q64">
-        <v>-0.3083130133333334</v>
+        <v>-0.3816836533333341</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1977438435452052</v>
+        <v>0.2018504339112918</v>
       </c>
       <c r="T64">
-        <v>1.301518102432222</v>
+        <v>1.336694267362823</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2579039878234848</v>
+        <v>0.2538102737310486</v>
       </c>
       <c r="W64">
-        <v>0.1089396945875124</v>
+        <v>0.1095406518162821</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8596799594116162</v>
+        <v>0.846034245770162</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1436952711914357</v>
+        <v>0.1447052711914357</v>
       </c>
       <c r="C65">
-        <v>10.8175300938759</v>
+        <v>9.544643547901778</v>
       </c>
       <c r="D65">
-        <v>54.7295300938759</v>
+        <v>54.17064354790178</v>
       </c>
       <c r="E65">
-        <v>1.281999999999996</v>
+        <v>1.995999999999995</v>
       </c>
       <c r="F65">
-        <v>44.98200000000001</v>
+        <v>45.69600000000001</v>
       </c>
       <c r="G65">
         <v>1.07</v>
@@ -6617,37 +6617,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M65">
-        <v>6.603357600000002</v>
+        <v>6.708172800000002</v>
       </c>
       <c r="N65">
-        <v>-1.016690933333334</v>
+        <v>-1.121506133333334</v>
       </c>
       <c r="O65">
-        <v>-0.3050072800000002</v>
+        <v>-0.3364518400000001</v>
       </c>
       <c r="P65">
-        <v>-0.7116836533333337</v>
+        <v>-0.7850542933333338</v>
       </c>
       <c r="Q65">
-        <v>-0.3816836533333341</v>
+        <v>-0.4550542933333341</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2018504339112918</v>
+        <v>0.2061851681866054</v>
       </c>
       <c r="T65">
-        <v>1.336694267362823</v>
+        <v>1.373824663678457</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2538102737310486</v>
+        <v>0.2498444882040009</v>
       </c>
       <c r="W65">
-        <v>0.1095406518162821</v>
+        <v>0.1101228291316527</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.846034245770162</v>
+        <v>0.8328149606800032</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1447052711914357</v>
+        <v>0.1457152711914357</v>
       </c>
       <c r="C66">
-        <v>9.544643547901778</v>
+        <v>8.283056083733726</v>
       </c>
       <c r="D66">
-        <v>54.17064354790178</v>
+        <v>53.62305608373373</v>
       </c>
       <c r="E66">
-        <v>1.995999999999995</v>
+        <v>2.709999999999994</v>
       </c>
       <c r="F66">
-        <v>45.69600000000001</v>
+        <v>46.41</v>
       </c>
       <c r="G66">
         <v>1.07</v>
@@ -6699,37 +6699,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M66">
-        <v>6.708172800000002</v>
+        <v>6.812988000000002</v>
       </c>
       <c r="N66">
-        <v>-1.121506133333334</v>
+        <v>-1.226321333333334</v>
       </c>
       <c r="O66">
-        <v>-0.3364518400000001</v>
+        <v>-0.3678964000000001</v>
       </c>
       <c r="P66">
-        <v>-0.7850542933333338</v>
+        <v>-0.8584249333333337</v>
       </c>
       <c r="Q66">
-        <v>-0.4550542933333341</v>
+        <v>-0.5284249333333341</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2061851681866054</v>
+        <v>0.2107676015633656</v>
       </c>
       <c r="T66">
-        <v>1.373824663678457</v>
+        <v>1.413076796926413</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2498444882040009</v>
+        <v>0.2460007268470163</v>
       </c>
       <c r="W66">
-        <v>0.1101228291316527</v>
+        <v>0.110687093298858</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8328149606800032</v>
+        <v>0.8200024228233878</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1457152711914357</v>
+        <v>0.1467252711914357</v>
       </c>
       <c r="C67">
-        <v>8.283056083733726</v>
+        <v>7.03242847792982</v>
       </c>
       <c r="D67">
-        <v>53.62305608373373</v>
+        <v>53.08642847792983</v>
       </c>
       <c r="E67">
-        <v>2.709999999999994</v>
+        <v>3.423999999999999</v>
       </c>
       <c r="F67">
-        <v>46.41</v>
+        <v>47.12400000000001</v>
       </c>
       <c r="G67">
         <v>1.07</v>
@@ -6781,37 +6781,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M67">
-        <v>6.812988000000002</v>
+        <v>6.917803200000002</v>
       </c>
       <c r="N67">
-        <v>-1.226321333333334</v>
+        <v>-1.331136533333334</v>
       </c>
       <c r="O67">
-        <v>-0.3678964000000001</v>
+        <v>-0.3993409600000001</v>
       </c>
       <c r="P67">
-        <v>-0.8584249333333337</v>
+        <v>-0.9317955733333336</v>
       </c>
       <c r="Q67">
-        <v>-0.5284249333333341</v>
+        <v>-0.601795573333334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2107676015633656</v>
+        <v>0.2156195898446411</v>
       </c>
       <c r="T67">
-        <v>1.413076796926413</v>
+        <v>1.454637879188954</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2460007268470163</v>
+        <v>0.24227344310691</v>
       </c>
       <c r="W67">
-        <v>0.110687093298858</v>
+        <v>0.1112342585519056</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8200024228233878</v>
+        <v>0.8075781436897</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1467252711914357</v>
+        <v>0.1868706677446184</v>
       </c>
       <c r="C68">
-        <v>7.03242847792982</v>
+        <v>-8.788721413050723</v>
       </c>
       <c r="D68">
-        <v>53.08642847792983</v>
+        <v>37.97927858694928</v>
       </c>
       <c r="E68">
-        <v>3.423999999999999</v>
+        <v>4.137999999999998</v>
       </c>
       <c r="F68">
-        <v>47.12400000000001</v>
+        <v>47.83800000000001</v>
       </c>
       <c r="G68">
         <v>1.07</v>
@@ -6863,45 +6863,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M68">
-        <v>6.917803200000002</v>
+        <v>9.605870400000002</v>
       </c>
       <c r="N68">
-        <v>-1.331136533333334</v>
+        <v>-4.019203733333335</v>
       </c>
       <c r="O68">
-        <v>-0.3993409600000001</v>
+        <v>-1.20576112</v>
       </c>
       <c r="P68">
-        <v>-0.9317955733333336</v>
+        <v>-2.813442613333335</v>
       </c>
       <c r="Q68">
-        <v>-0.601795573333334</v>
+        <v>-2.483442613333335</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2156195898446411</v>
+        <v>0.229721385152608</v>
       </c>
       <c r="T68">
-        <v>1.454637879188954</v>
+        <v>1.57543080795709</v>
       </c>
       <c r="U68">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.24227344310691</v>
+        <v>0.1744766408674429</v>
       </c>
       <c r="W68">
-        <v>0.1112342585519056</v>
+        <v>0.1657650905138175</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8075781436897</v>
+        <v>0.5815888028914763</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1868706677446184</v>
+        <v>0.1884206677446184</v>
       </c>
       <c r="C69">
-        <v>-8.788721413050723</v>
+        <v>-9.915479835379685</v>
       </c>
       <c r="D69">
-        <v>37.97927858694928</v>
+        <v>37.56652016462032</v>
       </c>
       <c r="E69">
-        <v>4.137999999999998</v>
+        <v>4.851999999999997</v>
       </c>
       <c r="F69">
-        <v>47.83800000000001</v>
+        <v>48.55200000000001</v>
       </c>
       <c r="G69">
         <v>1.07</v>
@@ -6945,37 +6945,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M69">
-        <v>9.605870400000002</v>
+        <v>9.749241600000001</v>
       </c>
       <c r="N69">
-        <v>-4.019203733333335</v>
+        <v>-4.162574933333334</v>
       </c>
       <c r="O69">
-        <v>-1.20576112</v>
+        <v>-1.24877248</v>
       </c>
       <c r="P69">
-        <v>-2.813442613333335</v>
+        <v>-2.913802453333334</v>
       </c>
       <c r="Q69">
-        <v>-2.483442613333335</v>
+        <v>-2.583802453333334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.229721385152608</v>
+        <v>0.235468928438627</v>
       </c>
       <c r="T69">
-        <v>1.57543080795709</v>
+        <v>1.62466302070575</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1744766408674429</v>
+        <v>0.1719108079135099</v>
       </c>
       <c r="W69">
-        <v>0.1657650905138175</v>
+        <v>0.1662803097709672</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5815888028914763</v>
+        <v>0.5730360263783665</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1884206677446184</v>
+        <v>0.1899706677446183</v>
       </c>
       <c r="C70">
-        <v>-9.915479835379685</v>
+        <v>-11.0333630050013</v>
       </c>
       <c r="D70">
-        <v>37.56652016462032</v>
+        <v>37.16263699499871</v>
       </c>
       <c r="E70">
-        <v>4.851999999999997</v>
+        <v>5.565999999999995</v>
       </c>
       <c r="F70">
-        <v>48.55200000000001</v>
+        <v>49.26600000000001</v>
       </c>
       <c r="G70">
         <v>1.07</v>
@@ -7027,37 +7027,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M70">
-        <v>9.749241600000001</v>
+        <v>9.892612800000002</v>
       </c>
       <c r="N70">
-        <v>-4.162574933333334</v>
+        <v>-4.305946133333334</v>
       </c>
       <c r="O70">
-        <v>-1.24877248</v>
+        <v>-1.29178384</v>
       </c>
       <c r="P70">
-        <v>-2.913802453333334</v>
+        <v>-3.014162293333334</v>
       </c>
       <c r="Q70">
-        <v>-2.583802453333334</v>
+        <v>-2.684162293333335</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.235468928438627</v>
+        <v>0.2415872809689053</v>
       </c>
       <c r="T70">
-        <v>1.62466302070575</v>
+        <v>1.677071505244645</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1719108079135099</v>
+        <v>0.1694193469292561</v>
       </c>
       <c r="W70">
-        <v>0.1662803097709672</v>
+        <v>0.1667805951366054</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5730360263783665</v>
+        <v>0.5647311564308538</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1899706677446183</v>
+        <v>0.1915206677446183</v>
       </c>
       <c r="C71">
-        <v>-11.0333630050013</v>
+        <v>-12.14265413448747</v>
       </c>
       <c r="D71">
-        <v>37.16263699499871</v>
+        <v>36.76734586551254</v>
       </c>
       <c r="E71">
-        <v>5.565999999999995</v>
+        <v>6.280000000000001</v>
       </c>
       <c r="F71">
-        <v>49.26600000000001</v>
+        <v>49.98000000000001</v>
       </c>
       <c r="G71">
         <v>1.07</v>
@@ -7109,37 +7109,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M71">
-        <v>9.892612800000002</v>
+        <v>10.035984</v>
       </c>
       <c r="N71">
-        <v>-4.305946133333334</v>
+        <v>-4.449317333333335</v>
       </c>
       <c r="O71">
-        <v>-1.29178384</v>
+        <v>-1.334795200000001</v>
       </c>
       <c r="P71">
-        <v>-3.014162293333334</v>
+        <v>-3.114522133333335</v>
       </c>
       <c r="Q71">
-        <v>-2.684162293333335</v>
+        <v>-2.784522133333335</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2415872809689053</v>
+        <v>0.2481135236678688</v>
       </c>
       <c r="T71">
-        <v>1.677071505244645</v>
+        <v>1.732973888752799</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1694193469292561</v>
+        <v>0.1669990705445525</v>
       </c>
       <c r="W71">
-        <v>0.1667805951366054</v>
+        <v>0.1672665866346539</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5647311564308538</v>
+        <v>0.5566635684818415</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1915206677446183</v>
+        <v>0.1930706677446183</v>
       </c>
       <c r="C72">
-        <v>-12.14265413448747</v>
+        <v>-13.24362451334369</v>
       </c>
       <c r="D72">
-        <v>36.76734586551254</v>
+        <v>36.38037548665632</v>
       </c>
       <c r="E72">
-        <v>6.280000000000001</v>
+        <v>6.994</v>
       </c>
       <c r="F72">
-        <v>49.98000000000001</v>
+        <v>50.69400000000001</v>
       </c>
       <c r="G72">
         <v>1.07</v>
@@ -7191,37 +7191,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M72">
-        <v>10.035984</v>
+        <v>10.1793552</v>
       </c>
       <c r="N72">
-        <v>-4.449317333333335</v>
+        <v>-4.592688533333334</v>
       </c>
       <c r="O72">
-        <v>-1.334795200000001</v>
+        <v>-1.37780656</v>
       </c>
       <c r="P72">
-        <v>-3.114522133333335</v>
+        <v>-3.214881973333334</v>
       </c>
       <c r="Q72">
-        <v>-2.784522133333335</v>
+        <v>-2.884881973333334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2481135236678688</v>
+        <v>0.2550898520702091</v>
       </c>
       <c r="T72">
-        <v>1.732973888752799</v>
+        <v>1.79273160905462</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1669990705445525</v>
+        <v>0.164646970959418</v>
       </c>
       <c r="W72">
-        <v>0.1672665866346539</v>
+        <v>0.1677388882313489</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5566635684818415</v>
+        <v>0.5488232365313932</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1930706677446183</v>
+        <v>0.1946206677446183</v>
       </c>
       <c r="C73">
-        <v>-13.24362451334368</v>
+        <v>-14.33653412891591</v>
       </c>
       <c r="D73">
-        <v>36.38037548665632</v>
+        <v>36.00146587108409</v>
       </c>
       <c r="E73">
-        <v>6.993999999999993</v>
+        <v>7.707999999999991</v>
       </c>
       <c r="F73">
-        <v>50.694</v>
+        <v>51.408</v>
       </c>
       <c r="G73">
         <v>1.07</v>
@@ -7273,37 +7273,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M73">
-        <v>10.1793552</v>
+        <v>10.3227264</v>
       </c>
       <c r="N73">
-        <v>-4.592688533333334</v>
+        <v>-4.736059733333333</v>
       </c>
       <c r="O73">
-        <v>-1.37780656</v>
+        <v>-1.42081792</v>
       </c>
       <c r="P73">
-        <v>-3.214881973333334</v>
+        <v>-3.315241813333333</v>
       </c>
       <c r="Q73">
-        <v>-2.884881973333334</v>
+        <v>-2.985241813333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.255089852070209</v>
+        <v>0.2625644896441451</v>
       </c>
       <c r="T73">
-        <v>1.792731609054619</v>
+        <v>1.856757737949427</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.164646970959418</v>
+        <v>0.1623602074738705</v>
       </c>
       <c r="W73">
-        <v>0.1677388882313489</v>
+        <v>0.1681980703392468</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5488232365313932</v>
+        <v>0.5412006915795683</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1946206677446183</v>
+        <v>0.1961706677446183</v>
       </c>
       <c r="C74">
-        <v>-14.33653412891591</v>
+        <v>-15.42163224889602</v>
       </c>
       <c r="D74">
-        <v>36.00146587108409</v>
+        <v>35.63036775110398</v>
       </c>
       <c r="E74">
-        <v>7.707999999999991</v>
+        <v>8.42199999999999</v>
       </c>
       <c r="F74">
-        <v>51.408</v>
+        <v>52.122</v>
       </c>
       <c r="G74">
         <v>1.07</v>
@@ -7355,37 +7355,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M74">
-        <v>10.3227264</v>
+        <v>10.4660976</v>
       </c>
       <c r="N74">
-        <v>-4.736059733333333</v>
+        <v>-4.879430933333332</v>
       </c>
       <c r="O74">
-        <v>-1.42081792</v>
+        <v>-1.463829279999999</v>
       </c>
       <c r="P74">
-        <v>-3.315241813333333</v>
+        <v>-3.415601653333332</v>
       </c>
       <c r="Q74">
-        <v>-2.985241813333333</v>
+        <v>-3.085601653333332</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2625644896441451</v>
+        <v>0.2705928040754097</v>
       </c>
       <c r="T74">
-        <v>1.856757737949427</v>
+        <v>1.925526543058665</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1623602074738705</v>
+        <v>0.1601360950427216</v>
       </c>
       <c r="W74">
-        <v>0.1681980703392468</v>
+        <v>0.1686446721154215</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5412006915795683</v>
+        <v>0.5337869834757387</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1961706677446183</v>
+        <v>0.1977206677446183</v>
       </c>
       <c r="C75">
-        <v>-15.42163224889602</v>
+        <v>-16.49915796816846</v>
       </c>
       <c r="D75">
-        <v>35.63036775110398</v>
+        <v>35.26684203183154</v>
       </c>
       <c r="E75">
-        <v>8.42199999999999</v>
+        <v>9.135999999999996</v>
       </c>
       <c r="F75">
-        <v>52.122</v>
+        <v>52.83600000000001</v>
       </c>
       <c r="G75">
         <v>1.07</v>
@@ -7437,37 +7437,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M75">
-        <v>10.4660976</v>
+        <v>10.6094688</v>
       </c>
       <c r="N75">
-        <v>-4.879430933333332</v>
+        <v>-5.022802133333334</v>
       </c>
       <c r="O75">
-        <v>-1.463829279999999</v>
+        <v>-1.50684064</v>
       </c>
       <c r="P75">
-        <v>-3.415601653333332</v>
+        <v>-3.515961493333334</v>
       </c>
       <c r="Q75">
-        <v>-3.085601653333332</v>
+        <v>-3.185961493333334</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2705928040754097</v>
+        <v>0.2792386811552331</v>
       </c>
       <c r="T75">
-        <v>1.925526543058665</v>
+        <v>1.99958525625323</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1601360950427216</v>
+        <v>0.1579720937583604</v>
       </c>
       <c r="W75">
-        <v>0.1686446721154215</v>
+        <v>0.1690792035733212</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5337869834757387</v>
+        <v>0.5265736458612016</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1977206677446183</v>
+        <v>0.1992706677446183</v>
       </c>
       <c r="C76">
-        <v>-16.49915796816846</v>
+        <v>-17.56934072251929</v>
       </c>
       <c r="D76">
-        <v>35.26684203183154</v>
+        <v>34.91065927748072</v>
       </c>
       <c r="E76">
-        <v>9.135999999999996</v>
+        <v>9.849999999999994</v>
       </c>
       <c r="F76">
-        <v>52.83600000000001</v>
+        <v>53.55</v>
       </c>
       <c r="G76">
         <v>1.07</v>
@@ -7519,37 +7519,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M76">
-        <v>10.6094688</v>
+        <v>10.75284</v>
       </c>
       <c r="N76">
-        <v>-5.022802133333334</v>
+        <v>-5.166173333333333</v>
       </c>
       <c r="O76">
-        <v>-1.50684064</v>
+        <v>-1.549852</v>
       </c>
       <c r="P76">
-        <v>-3.515961493333334</v>
+        <v>-3.616321333333333</v>
       </c>
       <c r="Q76">
-        <v>-3.185961493333334</v>
+        <v>-3.286321333333334</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2792386811552331</v>
+        <v>0.2885762284014425</v>
       </c>
       <c r="T76">
-        <v>1.99958525625323</v>
+        <v>2.079568666503359</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1579720937583604</v>
+        <v>0.1558657991749157</v>
       </c>
       <c r="W76">
-        <v>0.1690792035733212</v>
+        <v>0.1695021475256769</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5265736458612016</v>
+        <v>0.5195526639163855</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1992706677446183</v>
+        <v>0.2008206677446183</v>
       </c>
       <c r="C77">
-        <v>-17.56934072251929</v>
+        <v>-18.63240077152668</v>
       </c>
       <c r="D77">
-        <v>34.91065927748072</v>
+        <v>34.56159922847333</v>
       </c>
       <c r="E77">
-        <v>9.849999999999994</v>
+        <v>10.56399999999999</v>
       </c>
       <c r="F77">
-        <v>53.55</v>
+        <v>54.264</v>
       </c>
       <c r="G77">
         <v>1.07</v>
@@ -7601,37 +7601,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M77">
-        <v>10.75284</v>
+        <v>10.8962112</v>
       </c>
       <c r="N77">
-        <v>-5.166173333333333</v>
+        <v>-5.309544533333334</v>
       </c>
       <c r="O77">
-        <v>-1.549852</v>
+        <v>-1.59286336</v>
       </c>
       <c r="P77">
-        <v>-3.616321333333333</v>
+        <v>-3.716681173333334</v>
       </c>
       <c r="Q77">
-        <v>-3.286321333333334</v>
+        <v>-3.386681173333334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2885762284014425</v>
+        <v>0.298691904584836</v>
       </c>
       <c r="T77">
-        <v>2.079568666503359</v>
+        <v>2.166217360940999</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1558657991749157</v>
+        <v>0.1538149333962983</v>
       </c>
       <c r="W77">
-        <v>0.1695021475256769</v>
+        <v>0.1699139613740233</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5195526639163855</v>
+        <v>0.5127164446543278</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2008206677446183</v>
+        <v>0.2023706677446183</v>
       </c>
       <c r="C78">
-        <v>-18.63240077152668</v>
+        <v>-19.68854965276869</v>
       </c>
       <c r="D78">
-        <v>34.56159922847333</v>
+        <v>34.21945034723132</v>
       </c>
       <c r="E78">
-        <v>10.56399999999999</v>
+        <v>11.278</v>
       </c>
       <c r="F78">
-        <v>54.264</v>
+        <v>54.97800000000001</v>
       </c>
       <c r="G78">
         <v>1.07</v>
@@ -7683,37 +7683,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M78">
-        <v>10.8962112</v>
+        <v>11.0395824</v>
       </c>
       <c r="N78">
-        <v>-5.309544533333334</v>
+        <v>-5.452915733333334</v>
       </c>
       <c r="O78">
-        <v>-1.59286336</v>
+        <v>-1.63587472</v>
       </c>
       <c r="P78">
-        <v>-3.716681173333334</v>
+        <v>-3.817041013333334</v>
       </c>
       <c r="Q78">
-        <v>-3.386681173333334</v>
+        <v>-3.487041013333334</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.298691904584836</v>
+        <v>0.3096872047841767</v>
       </c>
       <c r="T78">
-        <v>2.166217360940999</v>
+        <v>2.260400724460173</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1538149333962983</v>
+        <v>0.1518173368586841</v>
       </c>
       <c r="W78">
-        <v>0.1699139613740233</v>
+        <v>0.1703150787587762</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5127164446543278</v>
+        <v>0.5060577895289469</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2023706677446183</v>
+        <v>0.2324132059510592</v>
       </c>
       <c r="C79">
-        <v>-19.68854965276869</v>
+        <v>-25.91147995178361</v>
       </c>
       <c r="D79">
-        <v>34.21945034723132</v>
+        <v>28.7105200482164</v>
       </c>
       <c r="E79">
-        <v>11.278</v>
+        <v>11.992</v>
       </c>
       <c r="F79">
-        <v>54.97800000000001</v>
+        <v>55.69200000000001</v>
       </c>
       <c r="G79">
         <v>1.07</v>
@@ -7765,45 +7765,45 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M79">
-        <v>11.0395824</v>
+        <v>13.1321736</v>
       </c>
       <c r="N79">
-        <v>-5.452915733333334</v>
+        <v>-7.545506933333334</v>
       </c>
       <c r="O79">
-        <v>-1.63587472</v>
+        <v>-2.26365208</v>
       </c>
       <c r="P79">
-        <v>-3.817041013333334</v>
+        <v>-5.281854853333334</v>
       </c>
       <c r="Q79">
-        <v>-3.487041013333334</v>
+        <v>-4.951854853333334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3096872047841767</v>
+        <v>0.3271027059400067</v>
       </c>
       <c r="T79">
-        <v>2.260400724460173</v>
+        <v>2.409578140855451</v>
       </c>
       <c r="U79">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1518173368586841</v>
+        <v>0.1276254831111888</v>
       </c>
       <c r="W79">
-        <v>0.1703150787587762</v>
+        <v>0.2057059110823817</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.5060577895289469</v>
+        <v>0.4254182770372962</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2324132059510592</v>
+        <v>0.2343132059510591</v>
       </c>
       <c r="C80">
-        <v>-25.91147995178361</v>
+        <v>-26.91484953635145</v>
       </c>
       <c r="D80">
-        <v>28.7105200482164</v>
+        <v>28.42115046364856</v>
       </c>
       <c r="E80">
-        <v>11.992</v>
+        <v>12.706</v>
       </c>
       <c r="F80">
-        <v>55.69200000000001</v>
+        <v>56.40600000000001</v>
       </c>
       <c r="G80">
         <v>1.07</v>
@@ -7847,37 +7847,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M80">
-        <v>13.1321736</v>
+        <v>13.3005348</v>
       </c>
       <c r="N80">
-        <v>-7.545506933333334</v>
+        <v>-7.713868133333333</v>
       </c>
       <c r="O80">
-        <v>-2.26365208</v>
+        <v>-2.31416044</v>
       </c>
       <c r="P80">
-        <v>-5.281854853333334</v>
+        <v>-5.399707693333333</v>
       </c>
       <c r="Q80">
-        <v>-4.951854853333334</v>
+        <v>-5.069707693333333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3271027059400067</v>
+        <v>0.3404980728895308</v>
       </c>
       <c r="T80">
-        <v>2.409578140855451</v>
+        <v>2.524319957086663</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1276254831111888</v>
+        <v>0.1260099706667434</v>
       </c>
       <c r="W80">
-        <v>0.2057059110823817</v>
+        <v>0.2060868489167819</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4254182770372962</v>
+        <v>0.4200332355558114</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2343132059510591</v>
+        <v>0.2362132059510592</v>
       </c>
       <c r="C81">
-        <v>-26.91484953635145</v>
+        <v>-27.9124442881504</v>
       </c>
       <c r="D81">
-        <v>28.42115046364856</v>
+        <v>28.1375557118496</v>
       </c>
       <c r="E81">
-        <v>12.706</v>
+        <v>13.41999999999999</v>
       </c>
       <c r="F81">
-        <v>56.40600000000001</v>
+        <v>57.12</v>
       </c>
       <c r="G81">
         <v>1.07</v>
@@ -7929,37 +7929,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M81">
-        <v>13.3005348</v>
+        <v>13.468896</v>
       </c>
       <c r="N81">
-        <v>-7.713868133333333</v>
+        <v>-7.882229333333333</v>
       </c>
       <c r="O81">
-        <v>-2.31416044</v>
+        <v>-2.3646688</v>
       </c>
       <c r="P81">
-        <v>-5.399707693333333</v>
+        <v>-5.517560533333333</v>
       </c>
       <c r="Q81">
-        <v>-5.069707693333333</v>
+        <v>-5.187560533333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3404980728895308</v>
+        <v>0.3552329765340074</v>
       </c>
       <c r="T81">
-        <v>2.524319957086663</v>
+        <v>2.650535954940996</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1260099706667434</v>
+        <v>0.1244348460334091</v>
       </c>
       <c r="W81">
-        <v>0.2060868489167819</v>
+        <v>0.2064582633053221</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4200332355558114</v>
+        <v>0.4147828201113638</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2362132059510592</v>
+        <v>0.2381132059510592</v>
       </c>
       <c r="C82">
-        <v>-27.9124442881504</v>
+        <v>-28.90443536831637</v>
       </c>
       <c r="D82">
-        <v>28.1375557118496</v>
+        <v>27.85956463168364</v>
       </c>
       <c r="E82">
-        <v>13.41999999999999</v>
+        <v>14.134</v>
       </c>
       <c r="F82">
-        <v>57.12</v>
+        <v>57.83400000000001</v>
       </c>
       <c r="G82">
         <v>1.07</v>
@@ -8011,37 +8011,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M82">
-        <v>13.468896</v>
+        <v>13.6372572</v>
       </c>
       <c r="N82">
-        <v>-7.882229333333333</v>
+        <v>-8.050590533333335</v>
       </c>
       <c r="O82">
-        <v>-2.3646688</v>
+        <v>-2.41517716</v>
       </c>
       <c r="P82">
-        <v>-5.517560533333333</v>
+        <v>-5.635413373333334</v>
       </c>
       <c r="Q82">
-        <v>-5.187560533333333</v>
+        <v>-5.305413373333334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3552329765340074</v>
+        <v>0.3715189226673762</v>
       </c>
       <c r="T82">
-        <v>2.650535954940996</v>
+        <v>2.790037847306313</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1244348460334091</v>
+        <v>0.12289861336633</v>
       </c>
       <c r="W82">
-        <v>0.2064582633053221</v>
+        <v>0.2068205069682194</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4147828201113638</v>
+        <v>0.4096620445544333</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2381132059510592</v>
+        <v>0.2400132059510592</v>
       </c>
       <c r="C83">
-        <v>-28.90443536831637</v>
+        <v>-29.89098724006467</v>
       </c>
       <c r="D83">
-        <v>27.85956463168364</v>
+        <v>27.58701275993534</v>
       </c>
       <c r="E83">
-        <v>14.134</v>
+        <v>14.848</v>
       </c>
       <c r="F83">
-        <v>57.83400000000001</v>
+        <v>58.54800000000001</v>
       </c>
       <c r="G83">
         <v>1.07</v>
@@ -8093,37 +8093,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M83">
-        <v>13.6372572</v>
+        <v>13.8056184</v>
       </c>
       <c r="N83">
-        <v>-8.050590533333335</v>
+        <v>-8.218951733333334</v>
       </c>
       <c r="O83">
-        <v>-2.41517716</v>
+        <v>-2.46568552</v>
       </c>
       <c r="P83">
-        <v>-5.635413373333334</v>
+        <v>-5.753266213333334</v>
       </c>
       <c r="Q83">
-        <v>-5.305413373333334</v>
+        <v>-5.423266213333335</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3715189226673762</v>
+        <v>0.3896144183711194</v>
       </c>
       <c r="T83">
-        <v>2.790037847306313</v>
+        <v>2.945039949934441</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.12289861336633</v>
+        <v>0.1213998497886918</v>
       </c>
       <c r="W83">
-        <v>0.2068205069682194</v>
+        <v>0.2071739154198265</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4096620445544333</v>
+        <v>0.4046661659623061</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2400132059510592</v>
+        <v>0.2419132059510592</v>
       </c>
       <c r="C84">
-        <v>-29.89098724006467</v>
+        <v>-30.87225799314673</v>
       </c>
       <c r="D84">
-        <v>27.58701275993534</v>
+        <v>27.31974200685328</v>
       </c>
       <c r="E84">
-        <v>14.848</v>
+        <v>15.562</v>
       </c>
       <c r="F84">
-        <v>58.54800000000001</v>
+        <v>59.26200000000001</v>
       </c>
       <c r="G84">
         <v>1.07</v>
@@ -8175,37 +8175,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M84">
-        <v>13.8056184</v>
+        <v>13.9739796</v>
       </c>
       <c r="N84">
-        <v>-8.218951733333334</v>
+        <v>-8.387312933333334</v>
       </c>
       <c r="O84">
-        <v>-2.46568552</v>
+        <v>-2.51619388</v>
       </c>
       <c r="P84">
-        <v>-5.753266213333334</v>
+        <v>-5.871119053333334</v>
       </c>
       <c r="Q84">
-        <v>-5.423266213333335</v>
+        <v>-5.541119053333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3896144183711194</v>
+        <v>0.4098387959223617</v>
       </c>
       <c r="T84">
-        <v>2.945039949934441</v>
+        <v>3.118277594048232</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1213998497886918</v>
+        <v>0.119937200996057</v>
       </c>
       <c r="W84">
-        <v>0.2071739154198265</v>
+        <v>0.2075188080051298</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4046661659623061</v>
+        <v>0.3997906699868566</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2419132059510592</v>
+        <v>0.2438132059510592</v>
       </c>
       <c r="C85">
-        <v>-30.87225799314673</v>
+        <v>-31.84839964962722</v>
       </c>
       <c r="D85">
-        <v>27.31974200685328</v>
+        <v>27.05760035037279</v>
       </c>
       <c r="E85">
-        <v>15.562</v>
+        <v>16.276</v>
       </c>
       <c r="F85">
-        <v>59.26200000000001</v>
+        <v>59.97600000000001</v>
       </c>
       <c r="G85">
         <v>1.07</v>
@@ -8257,37 +8257,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M85">
-        <v>13.9739796</v>
+        <v>14.1423408</v>
       </c>
       <c r="N85">
-        <v>-8.387312933333334</v>
+        <v>-8.555674133333335</v>
       </c>
       <c r="O85">
-        <v>-2.51619388</v>
+        <v>-2.566702240000001</v>
       </c>
       <c r="P85">
-        <v>-5.871119053333334</v>
+        <v>-5.988971893333335</v>
       </c>
       <c r="Q85">
-        <v>-5.541119053333334</v>
+        <v>-5.658971893333336</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4098387959223617</v>
+        <v>0.4325912206675094</v>
       </c>
       <c r="T85">
-        <v>3.118277594048232</v>
+        <v>3.313169943676247</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.119937200996057</v>
+        <v>0.1185093771746754</v>
       </c>
       <c r="W85">
-        <v>0.2075188080051298</v>
+        <v>0.2078554888622116</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3997906699868566</v>
+        <v>0.3950312572489179</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2438132059510592</v>
+        <v>0.2457132059510592</v>
       </c>
       <c r="C86">
-        <v>-31.8483996496272</v>
+        <v>-32.81955845222424</v>
       </c>
       <c r="D86">
-        <v>27.0576003503728</v>
+        <v>26.80044154777576</v>
       </c>
       <c r="E86">
-        <v>16.27599999999999</v>
+        <v>16.98999999999999</v>
       </c>
       <c r="F86">
-        <v>59.976</v>
+        <v>60.69</v>
       </c>
       <c r="G86">
         <v>1.07</v>
@@ -8339,37 +8339,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M86">
-        <v>14.1423408</v>
+        <v>14.310702</v>
       </c>
       <c r="N86">
-        <v>-8.555674133333332</v>
+        <v>-8.724035333333333</v>
       </c>
       <c r="O86">
-        <v>-2.566702239999999</v>
+        <v>-2.6172106</v>
       </c>
       <c r="P86">
-        <v>-5.988971893333332</v>
+        <v>-6.106824733333333</v>
       </c>
       <c r="Q86">
-        <v>-5.658971893333332</v>
+        <v>-5.776824733333333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4325912206675091</v>
+        <v>0.4583773020453431</v>
       </c>
       <c r="T86">
-        <v>3.313169943676245</v>
+        <v>3.534047939921328</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1185093771746754</v>
+        <v>0.1171151492079145</v>
       </c>
       <c r="W86">
-        <v>0.2078554888622116</v>
+        <v>0.2081842478167738</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.395031257248918</v>
+        <v>0.3903838306930483</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2457132059510592</v>
+        <v>0.2476132059510592</v>
       </c>
       <c r="C87">
-        <v>-32.81955845222424</v>
+        <v>-33.78587513636195</v>
       </c>
       <c r="D87">
-        <v>26.80044154777576</v>
+        <v>26.54812486363805</v>
       </c>
       <c r="E87">
-        <v>16.98999999999999</v>
+        <v>17.70399999999999</v>
       </c>
       <c r="F87">
-        <v>60.69</v>
+        <v>61.404</v>
       </c>
       <c r="G87">
         <v>1.07</v>
@@ -8421,37 +8421,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M87">
-        <v>14.310702</v>
+        <v>14.4790632</v>
       </c>
       <c r="N87">
-        <v>-8.724035333333333</v>
+        <v>-8.892396533333333</v>
       </c>
       <c r="O87">
-        <v>-2.6172106</v>
+        <v>-2.66771896</v>
       </c>
       <c r="P87">
-        <v>-6.106824733333333</v>
+        <v>-6.224677573333333</v>
       </c>
       <c r="Q87">
-        <v>-5.776824733333333</v>
+        <v>-5.894677573333333</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4583773020453431</v>
+        <v>0.4878471093342962</v>
       </c>
       <c r="T87">
-        <v>3.534047939921328</v>
+        <v>3.786479935629994</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1171151492079145</v>
+        <v>0.1157533451473573</v>
       </c>
       <c r="W87">
-        <v>0.2081842478167738</v>
+        <v>0.2085053612142531</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3903838306930483</v>
+        <v>0.3858444838245245</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2476132059510592</v>
+        <v>0.2495132059510592</v>
       </c>
       <c r="C88">
-        <v>-33.78587513636195</v>
+        <v>-34.74748518699867</v>
       </c>
       <c r="D88">
-        <v>26.54812486363805</v>
+        <v>26.30051481300133</v>
       </c>
       <c r="E88">
-        <v>17.70399999999999</v>
+        <v>18.41799999999999</v>
       </c>
       <c r="F88">
-        <v>61.404</v>
+        <v>62.118</v>
       </c>
       <c r="G88">
         <v>1.07</v>
@@ -8503,37 +8503,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M88">
-        <v>14.4790632</v>
+        <v>14.6474244</v>
       </c>
       <c r="N88">
-        <v>-8.892396533333333</v>
+        <v>-9.060757733333332</v>
       </c>
       <c r="O88">
-        <v>-2.66771896</v>
+        <v>-2.71822732</v>
       </c>
       <c r="P88">
-        <v>-6.224677573333333</v>
+        <v>-6.342530413333333</v>
       </c>
       <c r="Q88">
-        <v>-5.894677573333333</v>
+        <v>-6.012530413333334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4878471093342962</v>
+        <v>0.5218507331292419</v>
       </c>
       <c r="T88">
-        <v>3.786479935629994</v>
+        <v>4.077747622986147</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1157533451473573</v>
+        <v>0.1144228469272728</v>
       </c>
       <c r="W88">
-        <v>0.2085053612142531</v>
+        <v>0.2088190926945491</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3858444838245245</v>
+        <v>0.3814094897575759</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2495132059510592</v>
+        <v>0.2514132059510591</v>
       </c>
       <c r="C89">
-        <v>-34.74748518699867</v>
+        <v>-35.70451908121557</v>
       </c>
       <c r="D89">
-        <v>26.30051481300133</v>
+        <v>26.05748091878444</v>
       </c>
       <c r="E89">
-        <v>18.41799999999999</v>
+        <v>19.132</v>
       </c>
       <c r="F89">
-        <v>62.118</v>
+        <v>62.83200000000001</v>
       </c>
       <c r="G89">
         <v>1.07</v>
@@ -8585,37 +8585,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M89">
-        <v>14.6474244</v>
+        <v>14.8157856</v>
       </c>
       <c r="N89">
-        <v>-9.060757733333332</v>
+        <v>-9.229118933333334</v>
       </c>
       <c r="O89">
-        <v>-2.71822732</v>
+        <v>-2.76873568</v>
       </c>
       <c r="P89">
-        <v>-6.342530413333333</v>
+        <v>-6.460383253333333</v>
       </c>
       <c r="Q89">
-        <v>-6.012530413333334</v>
+        <v>-6.130383253333333</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5218507331292419</v>
+        <v>0.5615216275566788</v>
       </c>
       <c r="T89">
-        <v>4.077747622986147</v>
+        <v>4.41755992490166</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1144228469272728</v>
+        <v>0.1131225873030992</v>
       </c>
       <c r="W89">
-        <v>0.2088190926945491</v>
+        <v>0.2091256939139292</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3814094897575759</v>
+        <v>0.3770752910103307</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2514132059510591</v>
+        <v>0.2533132059510592</v>
       </c>
       <c r="C90">
-        <v>-35.70451908121557</v>
+        <v>-36.65710251747826</v>
       </c>
       <c r="D90">
-        <v>26.05748091878444</v>
+        <v>25.81889748252175</v>
       </c>
       <c r="E90">
-        <v>19.132</v>
+        <v>19.846</v>
       </c>
       <c r="F90">
-        <v>62.83200000000001</v>
+        <v>63.54600000000001</v>
       </c>
       <c r="G90">
         <v>1.07</v>
@@ -8667,37 +8667,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M90">
-        <v>14.8157856</v>
+        <v>14.9841468</v>
       </c>
       <c r="N90">
-        <v>-9.229118933333334</v>
+        <v>-9.397480133333334</v>
       </c>
       <c r="O90">
-        <v>-2.76873568</v>
+        <v>-2.81924404</v>
       </c>
       <c r="P90">
-        <v>-6.460383253333333</v>
+        <v>-6.578236093333333</v>
       </c>
       <c r="Q90">
-        <v>-6.130383253333333</v>
+        <v>-6.248236093333334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5615216275566788</v>
+        <v>0.6084054118800133</v>
       </c>
       <c r="T90">
-        <v>4.41755992490166</v>
+        <v>4.819156281710902</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1131225873030992</v>
+        <v>0.1118515469963228</v>
       </c>
       <c r="W90">
-        <v>0.2091256939139292</v>
+        <v>0.2094254052182671</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3770752910103307</v>
+        <v>0.3728384899877427</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2533132059510592</v>
+        <v>0.2552132059510592</v>
       </c>
       <c r="C91">
-        <v>-36.65710251747826</v>
+        <v>-37.60535663241815</v>
       </c>
       <c r="D91">
-        <v>25.81889748252175</v>
+        <v>25.58464336758186</v>
       </c>
       <c r="E91">
-        <v>19.846</v>
+        <v>20.56</v>
       </c>
       <c r="F91">
-        <v>63.54600000000001</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="G91">
         <v>1.07</v>
@@ -8749,37 +8749,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M91">
-        <v>14.9841468</v>
+        <v>15.152508</v>
       </c>
       <c r="N91">
-        <v>-9.397480133333334</v>
+        <v>-9.565841333333333</v>
       </c>
       <c r="O91">
-        <v>-2.81924404</v>
+        <v>-2.8697524</v>
       </c>
       <c r="P91">
-        <v>-6.578236093333333</v>
+        <v>-6.696088933333334</v>
       </c>
       <c r="Q91">
-        <v>-6.248236093333334</v>
+        <v>-6.366088933333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6084054118800133</v>
+        <v>0.6646659530680148</v>
       </c>
       <c r="T91">
-        <v>4.819156281710902</v>
+        <v>5.301071909881993</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1118515469963228</v>
+        <v>0.110608752029697</v>
       </c>
       <c r="W91">
-        <v>0.2094254052182671</v>
+        <v>0.2097184562713975</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3728384899877427</v>
+        <v>0.36869584009899</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2552132059510592</v>
+        <v>0.2571132059510592</v>
       </c>
       <c r="C92">
-        <v>-37.60535663241815</v>
+        <v>-38.54939820591859</v>
       </c>
       <c r="D92">
-        <v>25.58464336758186</v>
+        <v>25.35460179408141</v>
       </c>
       <c r="E92">
-        <v>20.56</v>
+        <v>21.27399999999999</v>
       </c>
       <c r="F92">
-        <v>64.26000000000001</v>
+        <v>64.974</v>
       </c>
       <c r="G92">
         <v>1.07</v>
@@ -8831,37 +8831,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M92">
-        <v>15.152508</v>
+        <v>15.3208692</v>
       </c>
       <c r="N92">
-        <v>-9.565841333333333</v>
+        <v>-9.734202533333333</v>
       </c>
       <c r="O92">
-        <v>-2.8697524</v>
+        <v>-2.92026076</v>
       </c>
       <c r="P92">
-        <v>-6.696088933333334</v>
+        <v>-6.813941773333333</v>
       </c>
       <c r="Q92">
-        <v>-6.366088933333334</v>
+        <v>-6.483941773333333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6646659530680148</v>
+        <v>0.7334288367422387</v>
       </c>
       <c r="T92">
-        <v>5.301071909881993</v>
+        <v>5.890079899868882</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.110608752029697</v>
+        <v>0.1093932712381619</v>
       </c>
       <c r="W92">
-        <v>0.2097184562713975</v>
+        <v>0.2100050666420414</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.36869584009899</v>
+        <v>0.3646442374605396</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2571132059510592</v>
+        <v>0.2590132059510592</v>
       </c>
       <c r="C93">
-        <v>-38.54939820591859</v>
+        <v>-39.48933985523563</v>
       </c>
       <c r="D93">
-        <v>25.35460179408141</v>
+        <v>25.12866014476438</v>
       </c>
       <c r="E93">
-        <v>21.27399999999999</v>
+        <v>21.98799999999999</v>
       </c>
       <c r="F93">
-        <v>64.974</v>
+        <v>65.688</v>
       </c>
       <c r="G93">
         <v>1.07</v>
@@ -8913,37 +8913,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M93">
-        <v>15.3208692</v>
+        <v>15.4892304</v>
       </c>
       <c r="N93">
-        <v>-9.734202533333333</v>
+        <v>-9.902563733333334</v>
       </c>
       <c r="O93">
-        <v>-2.92026076</v>
+        <v>-2.97076912</v>
       </c>
       <c r="P93">
-        <v>-6.813941773333333</v>
+        <v>-6.931794613333334</v>
       </c>
       <c r="Q93">
-        <v>-6.483941773333333</v>
+        <v>-6.601794613333334</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7334288367422387</v>
+        <v>0.8193824413350188</v>
       </c>
       <c r="T93">
-        <v>5.890079899868882</v>
+        <v>6.626339887352494</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1093932712381619</v>
+        <v>0.1082042139420949</v>
       </c>
       <c r="W93">
-        <v>0.2100050666420414</v>
+        <v>0.210285446352454</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3646442374605396</v>
+        <v>0.3606807131403164</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2590132059510592</v>
+        <v>0.2609132059510592</v>
       </c>
       <c r="C94">
-        <v>-39.48933985523563</v>
+        <v>-40.42529021883124</v>
       </c>
       <c r="D94">
-        <v>25.12866014476438</v>
+        <v>24.90670978116877</v>
       </c>
       <c r="E94">
-        <v>21.98799999999999</v>
+        <v>22.70200000000001</v>
       </c>
       <c r="F94">
-        <v>65.688</v>
+        <v>66.40200000000002</v>
       </c>
       <c r="G94">
         <v>1.07</v>
@@ -8995,37 +8995,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M94">
-        <v>15.4892304</v>
+        <v>15.6575916</v>
       </c>
       <c r="N94">
-        <v>-9.902563733333334</v>
+        <v>-10.07092493333334</v>
       </c>
       <c r="O94">
-        <v>-2.97076912</v>
+        <v>-3.021277480000001</v>
       </c>
       <c r="P94">
-        <v>-6.931794613333334</v>
+        <v>-7.049647453333336</v>
       </c>
       <c r="Q94">
-        <v>-6.601794613333334</v>
+        <v>-6.719647453333335</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8193824413350188</v>
+        <v>0.929894218668593</v>
       </c>
       <c r="T94">
-        <v>6.626339887352494</v>
+        <v>7.572959871259994</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1082042139420949</v>
+        <v>0.1070407277706745</v>
       </c>
       <c r="W94">
-        <v>0.210285446352454</v>
+        <v>0.210559796391675</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3606807131403164</v>
+        <v>0.3568024259022484</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2609132059510592</v>
+        <v>0.2628132059510592</v>
       </c>
       <c r="C95">
-        <v>-40.42529021883124</v>
+        <v>-41.35735413054955</v>
       </c>
       <c r="D95">
-        <v>24.90670978116877</v>
+        <v>24.68864586945046</v>
       </c>
       <c r="E95">
-        <v>22.70200000000001</v>
+        <v>23.416</v>
       </c>
       <c r="F95">
-        <v>66.40200000000002</v>
+        <v>67.11600000000001</v>
       </c>
       <c r="G95">
         <v>1.07</v>
@@ -9077,37 +9077,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M95">
-        <v>15.6575916</v>
+        <v>15.8259528</v>
       </c>
       <c r="N95">
-        <v>-10.07092493333334</v>
+        <v>-10.23928613333334</v>
       </c>
       <c r="O95">
-        <v>-3.021277480000001</v>
+        <v>-3.07178584</v>
       </c>
       <c r="P95">
-        <v>-7.049647453333336</v>
+        <v>-7.167500293333335</v>
       </c>
       <c r="Q95">
-        <v>-6.719647453333335</v>
+        <v>-6.837500293333335</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.929894218668593</v>
+        <v>1.077243255113359</v>
       </c>
       <c r="T95">
-        <v>7.572959871259994</v>
+        <v>8.835119849803329</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1070407277706745</v>
+        <v>0.105901996624178</v>
       </c>
       <c r="W95">
-        <v>0.210559796391675</v>
+        <v>0.2108283091960188</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3568024259022484</v>
+        <v>0.3530066554139266</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2628132059510592</v>
+        <v>0.2647132059510592</v>
       </c>
       <c r="C96">
-        <v>-41.35735413054955</v>
+        <v>-42.28563278472285</v>
       </c>
       <c r="D96">
-        <v>24.68864586945046</v>
+        <v>24.47436721527716</v>
       </c>
       <c r="E96">
-        <v>23.416</v>
+        <v>24.13</v>
       </c>
       <c r="F96">
-        <v>67.11600000000001</v>
+        <v>67.83000000000001</v>
       </c>
       <c r="G96">
         <v>1.07</v>
@@ -9159,37 +9159,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M96">
-        <v>15.8259528</v>
+        <v>15.994314</v>
       </c>
       <c r="N96">
-        <v>-10.23928613333334</v>
+        <v>-10.40764733333334</v>
       </c>
       <c r="O96">
-        <v>-3.07178584</v>
+        <v>-3.1222942</v>
       </c>
       <c r="P96">
-        <v>-7.167500293333335</v>
+        <v>-7.285353133333334</v>
       </c>
       <c r="Q96">
-        <v>-6.837500293333335</v>
+        <v>-6.955353133333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.077243255113359</v>
+        <v>1.283531906136031</v>
       </c>
       <c r="T96">
-        <v>8.835119849803329</v>
+        <v>10.602143819764</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.105901996624178</v>
+        <v>0.1047872387649761</v>
       </c>
       <c r="W96">
-        <v>0.2108283091960188</v>
+        <v>0.2110911690992187</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3530066554139266</v>
+        <v>0.3492907958832537</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2647132059510592</v>
+        <v>0.2666132059510591</v>
       </c>
       <c r="C97">
-        <v>-42.28563278472285</v>
+        <v>-43.21022389275346</v>
       </c>
       <c r="D97">
-        <v>24.47436721527716</v>
+        <v>24.26377610724655</v>
       </c>
       <c r="E97">
-        <v>24.13</v>
+        <v>24.844</v>
       </c>
       <c r="F97">
-        <v>67.83000000000001</v>
+        <v>68.54400000000001</v>
       </c>
       <c r="G97">
         <v>1.07</v>
@@ -9241,37 +9241,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M97">
-        <v>15.994314</v>
+        <v>16.1626752</v>
       </c>
       <c r="N97">
-        <v>-10.40764733333334</v>
+        <v>-10.57600853333333</v>
       </c>
       <c r="O97">
-        <v>-3.1222942</v>
+        <v>-3.17280256</v>
       </c>
       <c r="P97">
-        <v>-7.285353133333334</v>
+        <v>-7.403205973333334</v>
       </c>
       <c r="Q97">
-        <v>-6.955353133333334</v>
+        <v>-7.073205973333334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.283531906136031</v>
+        <v>1.592964882670039</v>
       </c>
       <c r="T97">
-        <v>10.602143819764</v>
+        <v>13.252679774705</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1047872387649761</v>
+        <v>0.1036957050278409</v>
       </c>
       <c r="W97">
-        <v>0.2110911690992187</v>
+        <v>0.2113485527544351</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3492907958832537</v>
+        <v>0.3456523500928032</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2666132059510591</v>
+        <v>0.2685132059510592</v>
       </c>
       <c r="C98">
-        <v>-43.21022389275345</v>
+        <v>-44.1312218316808</v>
       </c>
       <c r="D98">
-        <v>24.26377610724655</v>
+        <v>24.05677816831921</v>
       </c>
       <c r="E98">
-        <v>24.84399999999999</v>
+        <v>25.558</v>
       </c>
       <c r="F98">
-        <v>68.544</v>
+        <v>69.25800000000001</v>
       </c>
       <c r="G98">
         <v>1.07</v>
@@ -9323,37 +9323,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M98">
-        <v>16.1626752</v>
+        <v>16.3310364</v>
       </c>
       <c r="N98">
-        <v>-10.57600853333333</v>
+        <v>-10.74436973333333</v>
       </c>
       <c r="O98">
-        <v>-3.172802559999999</v>
+        <v>-3.22331092</v>
       </c>
       <c r="P98">
-        <v>-7.403205973333332</v>
+        <v>-7.521058813333334</v>
       </c>
       <c r="Q98">
-        <v>-7.073205973333332</v>
+        <v>-7.191058813333335</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.592964882670035</v>
+        <v>2.108686510226714</v>
       </c>
       <c r="T98">
-        <v>13.25267977470497</v>
+        <v>17.67023969960663</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.103695705027841</v>
+        <v>0.102626677140956</v>
       </c>
       <c r="W98">
-        <v>0.2113485527544351</v>
+        <v>0.2116006295301626</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3456523500928033</v>
+        <v>0.3420889238031866</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2685132059510592</v>
+        <v>0.2704132059510592</v>
       </c>
       <c r="C99">
-        <v>-44.1312218316808</v>
+        <v>-45.04871778520797</v>
       </c>
       <c r="D99">
-        <v>24.05677816831921</v>
+        <v>23.85328221479203</v>
       </c>
       <c r="E99">
-        <v>25.558</v>
+        <v>26.272</v>
       </c>
       <c r="F99">
-        <v>69.25800000000001</v>
+        <v>69.97200000000001</v>
       </c>
       <c r="G99">
         <v>1.07</v>
@@ -9405,37 +9405,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M99">
-        <v>16.3310364</v>
+        <v>16.4993976</v>
       </c>
       <c r="N99">
-        <v>-10.74436973333333</v>
+        <v>-10.91273093333333</v>
       </c>
       <c r="O99">
-        <v>-3.22331092</v>
+        <v>-3.27381928</v>
       </c>
       <c r="P99">
-        <v>-7.521058813333334</v>
+        <v>-7.638911653333334</v>
       </c>
       <c r="Q99">
-        <v>-7.191058813333335</v>
+        <v>-7.308911653333334</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.108686510226714</v>
+        <v>3.140129765340071</v>
       </c>
       <c r="T99">
-        <v>17.67023969960663</v>
+        <v>26.50535954940994</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.102626677140956</v>
+        <v>0.1015794661497217</v>
       </c>
       <c r="W99">
-        <v>0.2116006295301626</v>
+        <v>0.2118475618818956</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3420889238031866</v>
+        <v>0.3385982204990725</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2704132059510592</v>
+        <v>0.2723132059510592</v>
       </c>
       <c r="C100">
-        <v>-45.04871778520797</v>
+        <v>-45.96279987763086</v>
       </c>
       <c r="D100">
-        <v>23.85328221479203</v>
+        <v>23.65320012236914</v>
       </c>
       <c r="E100">
-        <v>26.272</v>
+        <v>26.986</v>
       </c>
       <c r="F100">
-        <v>69.97200000000001</v>
+        <v>70.68600000000001</v>
       </c>
       <c r="G100">
         <v>1.07</v>
@@ -9487,37 +9487,37 @@
         <v>5.586666666666668</v>
       </c>
       <c r="M100">
-        <v>16.4993976</v>
+        <v>16.6677588</v>
       </c>
       <c r="N100">
-        <v>-10.91273093333333</v>
+        <v>-11.08109213333333</v>
       </c>
       <c r="O100">
-        <v>-3.27381928</v>
+        <v>-3.32432764</v>
       </c>
       <c r="P100">
-        <v>-7.638911653333334</v>
+        <v>-7.756764493333334</v>
       </c>
       <c r="Q100">
-        <v>-7.308911653333334</v>
+        <v>-7.426764493333334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.140129765340071</v>
+        <v>6.234459530680142</v>
       </c>
       <c r="T100">
-        <v>26.50535954940994</v>
+        <v>53.01071909881988</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1015794661497217</v>
+        <v>0.1005534109360882</v>
       </c>
       <c r="W100">
-        <v>0.2118475618818956</v>
+        <v>0.2120895057012704</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3385982204990725</v>
+        <v>0.3351780364536273</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2723132059510592</v>
-      </c>
-      <c r="C101">
-        <v>-45.96279987763086</v>
-      </c>
-      <c r="D101">
-        <v>23.65320012236914</v>
-      </c>
-      <c r="E101">
-        <v>26.986</v>
-      </c>
-      <c r="F101">
-        <v>70.68600000000001</v>
-      </c>
-      <c r="G101">
-        <v>1.07</v>
-      </c>
-      <c r="H101">
-        <v>27.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.916666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.3299999999999996</v>
-      </c>
-      <c r="L101">
-        <v>5.586666666666668</v>
-      </c>
-      <c r="M101">
-        <v>16.6677588</v>
-      </c>
-      <c r="N101">
-        <v>-11.08109213333333</v>
-      </c>
-      <c r="O101">
-        <v>-3.32432764</v>
-      </c>
-      <c r="P101">
-        <v>-7.756764493333334</v>
-      </c>
-      <c r="Q101">
-        <v>-7.426764493333334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.234459530680142</v>
-      </c>
-      <c r="T101">
-        <v>53.01071909881988</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1005534109360882</v>
-      </c>
-      <c r="W101">
-        <v>0.2120895057012704</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3351780364536273</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
